--- a/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -724,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>28636400</v>
+        <v>28718200</v>
       </c>
       <c r="E8" s="3">
-        <v>15531800</v>
+        <v>15576200</v>
       </c>
       <c r="F8" s="3">
-        <v>12030500</v>
+        <v>12064900</v>
       </c>
       <c r="G8" s="3">
-        <v>29500100</v>
+        <v>29584400</v>
       </c>
       <c r="H8" s="3">
-        <v>28456300</v>
+        <v>28537600</v>
       </c>
       <c r="I8" s="3">
-        <v>28065700</v>
+        <v>28145900</v>
       </c>
       <c r="J8" s="3">
-        <v>26957900</v>
+        <v>27034900</v>
       </c>
       <c r="K8" s="3">
         <v>27181100</v>
@@ -766,25 +766,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15634900</v>
+        <v>15679500</v>
       </c>
       <c r="E9" s="3">
-        <v>8395700</v>
+        <v>8419700</v>
       </c>
       <c r="F9" s="3">
-        <v>7650300</v>
+        <v>7672200</v>
       </c>
       <c r="G9" s="3">
-        <v>14929600</v>
+        <v>14972300</v>
       </c>
       <c r="H9" s="3">
-        <v>14019300</v>
+        <v>14059300</v>
       </c>
       <c r="I9" s="3">
-        <v>14568300</v>
+        <v>14609900</v>
       </c>
       <c r="J9" s="3">
-        <v>15657600</v>
+        <v>15702400</v>
       </c>
       <c r="K9" s="3">
         <v>16938600</v>
@@ -808,25 +808,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13001600</v>
+        <v>13038700</v>
       </c>
       <c r="E10" s="3">
-        <v>7136000</v>
+        <v>7156400</v>
       </c>
       <c r="F10" s="3">
-        <v>4380100</v>
+        <v>4392700</v>
       </c>
       <c r="G10" s="3">
-        <v>14570500</v>
+        <v>14612100</v>
       </c>
       <c r="H10" s="3">
-        <v>14437000</v>
+        <v>14478300</v>
       </c>
       <c r="I10" s="3">
-        <v>13497400</v>
+        <v>13536000</v>
       </c>
       <c r="J10" s="3">
-        <v>11300300</v>
+        <v>11332600</v>
       </c>
       <c r="K10" s="3">
         <v>10242500</v>
@@ -952,25 +952,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>100900</v>
+        <v>101200</v>
       </c>
       <c r="E14" s="3">
-        <v>788800</v>
+        <v>791000</v>
       </c>
       <c r="F14" s="3">
-        <v>1678500</v>
+        <v>1683300</v>
       </c>
       <c r="G14" s="3">
-        <v>166000</v>
+        <v>166500</v>
       </c>
       <c r="H14" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="I14" s="3">
-        <v>2088600</v>
+        <v>2094600</v>
       </c>
       <c r="J14" s="3">
-        <v>156200</v>
+        <v>156700</v>
       </c>
       <c r="K14" s="3">
         <v>148100</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2925200</v>
+        <v>2933500</v>
       </c>
       <c r="E15" s="3">
-        <v>2726600</v>
+        <v>2734400</v>
       </c>
       <c r="F15" s="3">
-        <v>2968600</v>
+        <v>2977000</v>
       </c>
       <c r="G15" s="3">
-        <v>3191000</v>
+        <v>3200100</v>
       </c>
       <c r="H15" s="3">
-        <v>3114000</v>
+        <v>3122800</v>
       </c>
       <c r="I15" s="3">
-        <v>2990300</v>
+        <v>2998800</v>
       </c>
       <c r="J15" s="3">
-        <v>1704500</v>
+        <v>1709400</v>
       </c>
       <c r="K15" s="3">
         <v>1664200</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>27340900</v>
+        <v>27419000</v>
       </c>
       <c r="E17" s="3">
-        <v>18279000</v>
+        <v>18331200</v>
       </c>
       <c r="F17" s="3">
-        <v>18573000</v>
+        <v>18626100</v>
       </c>
       <c r="G17" s="3">
-        <v>28404200</v>
+        <v>28485400</v>
       </c>
       <c r="H17" s="3">
-        <v>26944900</v>
+        <v>27021900</v>
       </c>
       <c r="I17" s="3">
-        <v>28048300</v>
+        <v>28128500</v>
       </c>
       <c r="J17" s="3">
-        <v>25755700</v>
+        <v>25829300</v>
       </c>
       <c r="K17" s="3">
         <v>26032100</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1295500</v>
+        <v>1299200</v>
       </c>
       <c r="E18" s="3">
-        <v>-2747200</v>
+        <v>-2755100</v>
       </c>
       <c r="F18" s="3">
-        <v>-6542600</v>
+        <v>-6561200</v>
       </c>
       <c r="G18" s="3">
-        <v>1095900</v>
+        <v>1099000</v>
       </c>
       <c r="H18" s="3">
-        <v>1511400</v>
+        <v>1515700</v>
       </c>
       <c r="I18" s="3">
         <v>17400</v>
       </c>
       <c r="J18" s="3">
-        <v>1202200</v>
+        <v>1205600</v>
       </c>
       <c r="K18" s="3">
         <v>1149000</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-330900</v>
+        <v>-331900</v>
       </c>
       <c r="E20" s="3">
-        <v>-516500</v>
+        <v>-517900</v>
       </c>
       <c r="F20" s="3">
-        <v>-556600</v>
+        <v>-558200</v>
       </c>
       <c r="G20" s="3">
-        <v>-277800</v>
+        <v>-278600</v>
       </c>
       <c r="H20" s="3">
-        <v>-355900</v>
+        <v>-356900</v>
       </c>
       <c r="I20" s="3">
-        <v>669400</v>
+        <v>671400</v>
       </c>
       <c r="J20" s="3">
-        <v>-60800</v>
+        <v>-60900</v>
       </c>
       <c r="K20" s="3">
         <v>-672900</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3591500</v>
+        <v>3618400</v>
       </c>
       <c r="E21" s="3">
-        <v>-692100</v>
+        <v>-677700</v>
       </c>
       <c r="F21" s="3">
-        <v>-3998300</v>
+        <v>-3990000</v>
       </c>
       <c r="G21" s="3">
-        <v>4057800</v>
+        <v>4090000</v>
       </c>
       <c r="H21" s="3">
-        <v>4287800</v>
+        <v>4320000</v>
       </c>
       <c r="I21" s="3">
-        <v>3767100</v>
+        <v>3797400</v>
       </c>
       <c r="J21" s="3">
-        <v>2947300</v>
+        <v>2967200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1237,25 +1237,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>593500</v>
+        <v>595200</v>
       </c>
       <c r="E22" s="3">
-        <v>587000</v>
+        <v>588700</v>
       </c>
       <c r="F22" s="3">
-        <v>450300</v>
+        <v>451600</v>
       </c>
       <c r="G22" s="3">
-        <v>442700</v>
+        <v>443900</v>
       </c>
       <c r="H22" s="3">
-        <v>470900</v>
+        <v>472200</v>
       </c>
       <c r="I22" s="3">
-        <v>546800</v>
+        <v>548400</v>
       </c>
       <c r="J22" s="3">
-        <v>248500</v>
+        <v>249200</v>
       </c>
       <c r="K22" s="3">
         <v>300500</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>371100</v>
+        <v>372100</v>
       </c>
       <c r="E23" s="3">
-        <v>-3850700</v>
+        <v>-3861700</v>
       </c>
       <c r="F23" s="3">
-        <v>-7549400</v>
+        <v>-7571000</v>
       </c>
       <c r="G23" s="3">
-        <v>375400</v>
+        <v>376500</v>
       </c>
       <c r="H23" s="3">
-        <v>684600</v>
+        <v>686600</v>
       </c>
       <c r="I23" s="3">
-        <v>140000</v>
+        <v>140400</v>
       </c>
       <c r="J23" s="3">
-        <v>893000</v>
+        <v>895500</v>
       </c>
       <c r="K23" s="3">
         <v>175600</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-423200</v>
+        <v>-424400</v>
       </c>
       <c r="E24" s="3">
-        <v>-306000</v>
+        <v>-306800</v>
       </c>
       <c r="F24" s="3">
-        <v>96600</v>
+        <v>96800</v>
       </c>
       <c r="G24" s="3">
-        <v>82500</v>
+        <v>82700</v>
       </c>
       <c r="H24" s="3">
-        <v>243000</v>
+        <v>243700</v>
       </c>
       <c r="I24" s="3">
-        <v>-22800</v>
+        <v>-22900</v>
       </c>
       <c r="J24" s="3">
-        <v>319000</v>
+        <v>319900</v>
       </c>
       <c r="K24" s="3">
         <v>31700</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>794200</v>
+        <v>796500</v>
       </c>
       <c r="E26" s="3">
-        <v>-3544700</v>
+        <v>-3554800</v>
       </c>
       <c r="F26" s="3">
-        <v>-7646000</v>
+        <v>-7667800</v>
       </c>
       <c r="G26" s="3">
-        <v>293000</v>
+        <v>293800</v>
       </c>
       <c r="H26" s="3">
-        <v>441600</v>
+        <v>442900</v>
       </c>
       <c r="I26" s="3">
-        <v>162800</v>
+        <v>163200</v>
       </c>
       <c r="J26" s="3">
-        <v>574000</v>
+        <v>575600</v>
       </c>
       <c r="K26" s="3">
         <v>143900</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>641200</v>
+        <v>643100</v>
       </c>
       <c r="E27" s="3">
-        <v>-3735700</v>
+        <v>-3746300</v>
       </c>
       <c r="F27" s="3">
-        <v>-7703500</v>
+        <v>-7725500</v>
       </c>
       <c r="G27" s="3">
-        <v>296200</v>
+        <v>297100</v>
       </c>
       <c r="H27" s="3">
-        <v>428600</v>
+        <v>429800</v>
       </c>
       <c r="I27" s="3">
-        <v>158400</v>
+        <v>158900</v>
       </c>
       <c r="J27" s="3">
-        <v>566400</v>
+        <v>568000</v>
       </c>
       <c r="K27" s="3">
         <v>78300</v>
@@ -1549,7 +1549,7 @@
         <v>-8700</v>
       </c>
       <c r="J29" s="3">
-        <v>293000</v>
+        <v>293800</v>
       </c>
       <c r="K29" s="3">
         <v>27500</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>330900</v>
+        <v>331900</v>
       </c>
       <c r="E32" s="3">
-        <v>516500</v>
+        <v>517900</v>
       </c>
       <c r="F32" s="3">
-        <v>556600</v>
+        <v>558200</v>
       </c>
       <c r="G32" s="3">
-        <v>277800</v>
+        <v>278600</v>
       </c>
       <c r="H32" s="3">
-        <v>355900</v>
+        <v>356900</v>
       </c>
       <c r="I32" s="3">
-        <v>-669400</v>
+        <v>-671400</v>
       </c>
       <c r="J32" s="3">
-        <v>60800</v>
+        <v>60900</v>
       </c>
       <c r="K32" s="3">
         <v>672900</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>641200</v>
+        <v>643100</v>
       </c>
       <c r="E33" s="3">
-        <v>-3735700</v>
+        <v>-3746300</v>
       </c>
       <c r="F33" s="3">
-        <v>-7703500</v>
+        <v>-7725500</v>
       </c>
       <c r="G33" s="3">
-        <v>296200</v>
+        <v>297100</v>
       </c>
       <c r="H33" s="3">
-        <v>428600</v>
+        <v>429800</v>
       </c>
       <c r="I33" s="3">
-        <v>149700</v>
+        <v>150200</v>
       </c>
       <c r="J33" s="3">
-        <v>859300</v>
+        <v>861800</v>
       </c>
       <c r="K33" s="3">
         <v>105800</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>641200</v>
+        <v>643100</v>
       </c>
       <c r="E35" s="3">
-        <v>-3735700</v>
+        <v>-3746300</v>
       </c>
       <c r="F35" s="3">
-        <v>-7703500</v>
+        <v>-7725500</v>
       </c>
       <c r="G35" s="3">
-        <v>296200</v>
+        <v>297100</v>
       </c>
       <c r="H35" s="3">
-        <v>428600</v>
+        <v>429800</v>
       </c>
       <c r="I35" s="3">
-        <v>149700</v>
+        <v>150200</v>
       </c>
       <c r="J35" s="3">
-        <v>859300</v>
+        <v>861800</v>
       </c>
       <c r="K35" s="3">
         <v>105800</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>14378400</v>
+        <v>14419500</v>
       </c>
       <c r="E41" s="3">
-        <v>7223900</v>
+        <v>7244600</v>
       </c>
       <c r="F41" s="3">
-        <v>6969000</v>
+        <v>6988900</v>
       </c>
       <c r="G41" s="3">
-        <v>4030800</v>
+        <v>4042300</v>
       </c>
       <c r="H41" s="3">
-        <v>3889700</v>
+        <v>3900800</v>
       </c>
       <c r="I41" s="3">
-        <v>10141500</v>
+        <v>10170500</v>
       </c>
       <c r="J41" s="3">
-        <v>4272700</v>
+        <v>4284900</v>
       </c>
       <c r="K41" s="3">
         <v>3284000</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>672700</v>
+        <v>674600</v>
       </c>
       <c r="E42" s="3">
-        <v>525100</v>
+        <v>526600</v>
       </c>
       <c r="F42" s="3">
-        <v>658600</v>
+        <v>660500</v>
       </c>
       <c r="G42" s="3">
-        <v>868000</v>
+        <v>870500</v>
       </c>
       <c r="H42" s="3">
-        <v>352600</v>
+        <v>353600</v>
       </c>
       <c r="I42" s="3">
-        <v>456800</v>
+        <v>458100</v>
       </c>
       <c r="J42" s="3">
-        <v>141000</v>
+        <v>141500</v>
       </c>
       <c r="K42" s="3">
         <v>1023100</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4438700</v>
+        <v>4451400</v>
       </c>
       <c r="E43" s="3">
-        <v>2369600</v>
+        <v>2376400</v>
       </c>
       <c r="F43" s="3">
-        <v>2107100</v>
+        <v>2113100</v>
       </c>
       <c r="G43" s="3">
-        <v>2939300</v>
+        <v>2947700</v>
       </c>
       <c r="H43" s="3">
-        <v>2920800</v>
+        <v>2929200</v>
       </c>
       <c r="I43" s="3">
-        <v>5177600</v>
+        <v>5192400</v>
       </c>
       <c r="J43" s="3">
-        <v>2453200</v>
+        <v>2460200</v>
       </c>
       <c r="K43" s="3">
         <v>2354100</v>
@@ -2034,25 +2034,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1568900</v>
+        <v>1573400</v>
       </c>
       <c r="E44" s="3">
-        <v>615200</v>
+        <v>617000</v>
       </c>
       <c r="F44" s="3">
-        <v>589200</v>
+        <v>590800</v>
       </c>
       <c r="G44" s="3">
-        <v>799600</v>
+        <v>801900</v>
       </c>
       <c r="H44" s="3">
-        <v>686800</v>
+        <v>688800</v>
       </c>
       <c r="I44" s="3">
-        <v>1208700</v>
+        <v>1212100</v>
       </c>
       <c r="J44" s="3">
-        <v>614100</v>
+        <v>615900</v>
       </c>
       <c r="K44" s="3">
         <v>562900</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1856400</v>
+        <v>1861700</v>
       </c>
       <c r="E45" s="3">
-        <v>907100</v>
+        <v>909700</v>
       </c>
       <c r="F45" s="3">
-        <v>412300</v>
+        <v>413500</v>
       </c>
       <c r="G45" s="3">
-        <v>627100</v>
+        <v>628900</v>
       </c>
       <c r="H45" s="3">
-        <v>611900</v>
+        <v>613700</v>
       </c>
       <c r="I45" s="3">
-        <v>2214500</v>
+        <v>2220800</v>
       </c>
       <c r="J45" s="3">
-        <v>772500</v>
+        <v>774700</v>
       </c>
       <c r="K45" s="3">
         <v>758600</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12085800</v>
+        <v>12120300</v>
       </c>
       <c r="E46" s="3">
-        <v>11641000</v>
+        <v>11674200</v>
       </c>
       <c r="F46" s="3">
-        <v>10736100</v>
+        <v>10766700</v>
       </c>
       <c r="G46" s="3">
-        <v>9264800</v>
+        <v>9291300</v>
       </c>
       <c r="H46" s="3">
-        <v>8461900</v>
+        <v>8486100</v>
       </c>
       <c r="I46" s="3">
-        <v>9827900</v>
+        <v>9856000</v>
       </c>
       <c r="J46" s="3">
-        <v>8253600</v>
+        <v>8277200</v>
       </c>
       <c r="K46" s="3">
         <v>7982600</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1414800</v>
+        <v>1418900</v>
       </c>
       <c r="E47" s="3">
-        <v>1150100</v>
+        <v>1153400</v>
       </c>
       <c r="F47" s="3">
-        <v>1120800</v>
+        <v>1124000</v>
       </c>
       <c r="G47" s="3">
-        <v>1525500</v>
+        <v>1529900</v>
       </c>
       <c r="H47" s="3">
-        <v>1962800</v>
+        <v>1968400</v>
       </c>
       <c r="I47" s="3">
-        <v>1710000</v>
+        <v>1714800</v>
       </c>
       <c r="J47" s="3">
-        <v>1519000</v>
+        <v>1523300</v>
       </c>
       <c r="K47" s="3">
         <v>1424100</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>37794900</v>
+        <v>37902900</v>
       </c>
       <c r="E48" s="3">
-        <v>18462400</v>
+        <v>18515100</v>
       </c>
       <c r="F48" s="3">
-        <v>18723800</v>
+        <v>18777300</v>
       </c>
       <c r="G48" s="3">
-        <v>19624400</v>
+        <v>19680500</v>
       </c>
       <c r="H48" s="3">
-        <v>18960400</v>
+        <v>19014500</v>
       </c>
       <c r="I48" s="3">
-        <v>37986900</v>
+        <v>38095500</v>
       </c>
       <c r="J48" s="3">
-        <v>11499900</v>
+        <v>11532800</v>
       </c>
       <c r="K48" s="3">
         <v>11017000</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3161700</v>
+        <v>3170700</v>
       </c>
       <c r="E49" s="3">
-        <v>1580800</v>
+        <v>1585400</v>
       </c>
       <c r="F49" s="3">
-        <v>1567800</v>
+        <v>1572300</v>
       </c>
       <c r="G49" s="3">
-        <v>1651400</v>
+        <v>1656100</v>
       </c>
       <c r="H49" s="3">
-        <v>1530900</v>
+        <v>1535300</v>
       </c>
       <c r="I49" s="3">
-        <v>2903500</v>
+        <v>2911800</v>
       </c>
       <c r="J49" s="3">
-        <v>1393100</v>
+        <v>1397100</v>
       </c>
       <c r="K49" s="3">
         <v>1338400</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1185900</v>
+        <v>1189300</v>
       </c>
       <c r="E52" s="3">
-        <v>456800</v>
+        <v>458100</v>
       </c>
       <c r="F52" s="3">
-        <v>602200</v>
+        <v>603900</v>
       </c>
       <c r="G52" s="3">
-        <v>1281400</v>
+        <v>1285000</v>
       </c>
       <c r="H52" s="3">
-        <v>1240200</v>
+        <v>1243700</v>
       </c>
       <c r="I52" s="3">
-        <v>1575400</v>
+        <v>1579900</v>
       </c>
       <c r="J52" s="3">
-        <v>2215600</v>
+        <v>2221900</v>
       </c>
       <c r="K52" s="3">
         <v>2926400</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>35050900</v>
+        <v>35151100</v>
       </c>
       <c r="E54" s="3">
-        <v>33291100</v>
+        <v>33386200</v>
       </c>
       <c r="F54" s="3">
-        <v>32746400</v>
+        <v>32839900</v>
       </c>
       <c r="G54" s="3">
-        <v>33347500</v>
+        <v>33442800</v>
       </c>
       <c r="H54" s="3">
-        <v>32156100</v>
+        <v>32248000</v>
       </c>
       <c r="I54" s="3">
-        <v>32509900</v>
+        <v>32602700</v>
       </c>
       <c r="J54" s="3">
-        <v>24881200</v>
+        <v>24952300</v>
       </c>
       <c r="K54" s="3">
         <v>24688400</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2630000</v>
+        <v>2637600</v>
       </c>
       <c r="E57" s="3">
-        <v>2007300</v>
+        <v>2013000</v>
       </c>
       <c r="F57" s="3">
-        <v>1557000</v>
+        <v>1561400</v>
       </c>
       <c r="G57" s="3">
-        <v>2581200</v>
+        <v>2588600</v>
       </c>
       <c r="H57" s="3">
-        <v>2662600</v>
+        <v>2670200</v>
       </c>
       <c r="I57" s="3">
-        <v>2566000</v>
+        <v>2573400</v>
       </c>
       <c r="J57" s="3">
-        <v>2559500</v>
+        <v>2566800</v>
       </c>
       <c r="K57" s="3">
         <v>2533900</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3966800</v>
+        <v>3978100</v>
       </c>
       <c r="E58" s="3">
-        <v>2079900</v>
+        <v>2085900</v>
       </c>
       <c r="F58" s="3">
-        <v>2225300</v>
+        <v>2231700</v>
       </c>
       <c r="G58" s="3">
-        <v>1904200</v>
+        <v>1909600</v>
       </c>
       <c r="H58" s="3">
-        <v>1904200</v>
+        <v>1909600</v>
       </c>
       <c r="I58" s="3">
-        <v>3992800</v>
+        <v>4004200</v>
       </c>
       <c r="J58" s="3">
-        <v>1016600</v>
+        <v>1019500</v>
       </c>
       <c r="K58" s="3">
         <v>2036700</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10413800</v>
+        <v>10443600</v>
       </c>
       <c r="E59" s="3">
-        <v>8635500</v>
+        <v>8660200</v>
       </c>
       <c r="F59" s="3">
-        <v>8996800</v>
+        <v>9022500</v>
       </c>
       <c r="G59" s="3">
-        <v>9238800</v>
+        <v>9265200</v>
       </c>
       <c r="H59" s="3">
-        <v>8824300</v>
+        <v>8849500</v>
       </c>
       <c r="I59" s="3">
-        <v>11535700</v>
+        <v>11568700</v>
       </c>
       <c r="J59" s="3">
-        <v>7426800</v>
+        <v>7448000</v>
       </c>
       <c r="K59" s="3">
         <v>8124400</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14823300</v>
+        <v>14865600</v>
       </c>
       <c r="E60" s="3">
-        <v>12722700</v>
+        <v>12759100</v>
       </c>
       <c r="F60" s="3">
-        <v>12779100</v>
+        <v>12815600</v>
       </c>
       <c r="G60" s="3">
-        <v>13724200</v>
+        <v>13763400</v>
       </c>
       <c r="H60" s="3">
-        <v>13391100</v>
+        <v>13429300</v>
       </c>
       <c r="I60" s="3">
-        <v>13078600</v>
+        <v>13116000</v>
       </c>
       <c r="J60" s="3">
-        <v>11003000</v>
+        <v>11034400</v>
       </c>
       <c r="K60" s="3">
         <v>12694900</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14076800</v>
+        <v>14117000</v>
       </c>
       <c r="E61" s="3">
-        <v>15403700</v>
+        <v>15447800</v>
       </c>
       <c r="F61" s="3">
-        <v>18006700</v>
+        <v>18058100</v>
       </c>
       <c r="G61" s="3">
-        <v>10220700</v>
+        <v>10249900</v>
       </c>
       <c r="H61" s="3">
-        <v>10066600</v>
+        <v>10095400</v>
       </c>
       <c r="I61" s="3">
-        <v>10697000</v>
+        <v>10727600</v>
       </c>
       <c r="J61" s="3">
-        <v>8062600</v>
+        <v>8085700</v>
       </c>
       <c r="K61" s="3">
         <v>7469500</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13343300</v>
+        <v>13381500</v>
       </c>
       <c r="E62" s="3">
-        <v>9305000</v>
+        <v>9331500</v>
       </c>
       <c r="F62" s="3">
-        <v>7756700</v>
+        <v>7778800</v>
       </c>
       <c r="G62" s="3">
-        <v>6908200</v>
+        <v>6927900</v>
       </c>
       <c r="H62" s="3">
-        <v>6747600</v>
+        <v>6766900</v>
       </c>
       <c r="I62" s="3">
-        <v>6500200</v>
+        <v>6518800</v>
       </c>
       <c r="J62" s="3">
-        <v>4409400</v>
+        <v>4422000</v>
       </c>
       <c r="K62" s="3">
         <v>4235200</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>38310300</v>
+        <v>38419700</v>
       </c>
       <c r="E66" s="3">
-        <v>37440100</v>
+        <v>37547100</v>
       </c>
       <c r="F66" s="3">
-        <v>38552200</v>
+        <v>38662400</v>
       </c>
       <c r="G66" s="3">
-        <v>30869300</v>
+        <v>30957500</v>
       </c>
       <c r="H66" s="3">
-        <v>30218300</v>
+        <v>30304700</v>
       </c>
       <c r="I66" s="3">
-        <v>29897200</v>
+        <v>29982600</v>
       </c>
       <c r="J66" s="3">
-        <v>23488100</v>
+        <v>23555200</v>
       </c>
       <c r="K66" s="3">
         <v>24450400</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-24844300</v>
+        <v>-24915300</v>
       </c>
       <c r="E72" s="3">
-        <v>-12790000</v>
+        <v>-12826500</v>
       </c>
       <c r="F72" s="3">
-        <v>-8835200</v>
+        <v>-8860400</v>
       </c>
       <c r="G72" s="3">
-        <v>-1061100</v>
+        <v>-1064200</v>
       </c>
       <c r="H72" s="3">
-        <v>-1396400</v>
+        <v>-1400400</v>
       </c>
       <c r="I72" s="3">
-        <v>-4562400</v>
+        <v>-4575500</v>
       </c>
       <c r="J72" s="3">
-        <v>337400</v>
+        <v>338400</v>
       </c>
       <c r="K72" s="3">
         <v>-480300</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-3259300</v>
+        <v>-3268700</v>
       </c>
       <c r="E76" s="3">
-        <v>-4149000</v>
+        <v>-4160900</v>
       </c>
       <c r="F76" s="3">
-        <v>-5805800</v>
+        <v>-5822400</v>
       </c>
       <c r="G76" s="3">
-        <v>2478100</v>
+        <v>2485200</v>
       </c>
       <c r="H76" s="3">
-        <v>1937800</v>
+        <v>1943300</v>
       </c>
       <c r="I76" s="3">
-        <v>2612700</v>
+        <v>2620100</v>
       </c>
       <c r="J76" s="3">
-        <v>1393100</v>
+        <v>1397100</v>
       </c>
       <c r="K76" s="3">
         <v>238100</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>641200</v>
+        <v>643100</v>
       </c>
       <c r="E81" s="3">
-        <v>-3735700</v>
+        <v>-3746300</v>
       </c>
       <c r="F81" s="3">
-        <v>-7703500</v>
+        <v>-7725500</v>
       </c>
       <c r="G81" s="3">
-        <v>296200</v>
+        <v>297100</v>
       </c>
       <c r="H81" s="3">
-        <v>428600</v>
+        <v>429800</v>
       </c>
       <c r="I81" s="3">
-        <v>149700</v>
+        <v>150200</v>
       </c>
       <c r="J81" s="3">
-        <v>859300</v>
+        <v>861800</v>
       </c>
       <c r="K81" s="3">
         <v>105800</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2627900</v>
+        <v>2635400</v>
       </c>
       <c r="E83" s="3">
-        <v>2572500</v>
+        <v>2579900</v>
       </c>
       <c r="F83" s="3">
-        <v>3102000</v>
+        <v>3110900</v>
       </c>
       <c r="G83" s="3">
-        <v>3240900</v>
+        <v>3250200</v>
       </c>
       <c r="H83" s="3">
-        <v>3133500</v>
+        <v>3142400</v>
       </c>
       <c r="I83" s="3">
-        <v>3081400</v>
+        <v>3090200</v>
       </c>
       <c r="J83" s="3">
-        <v>1806500</v>
+        <v>1811700</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5268800</v>
+        <v>5283800</v>
       </c>
       <c r="E89" s="3">
-        <v>1664400</v>
+        <v>1669100</v>
       </c>
       <c r="F89" s="3">
-        <v>-3066200</v>
+        <v>-3075000</v>
       </c>
       <c r="G89" s="3">
-        <v>4226100</v>
+        <v>4238100</v>
       </c>
       <c r="H89" s="3">
-        <v>4120800</v>
+        <v>4132600</v>
       </c>
       <c r="I89" s="3">
-        <v>4447400</v>
+        <v>4460100</v>
       </c>
       <c r="J89" s="3">
-        <v>2429300</v>
+        <v>2436300</v>
       </c>
       <c r="K89" s="3">
         <v>1077000</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3224600</v>
+        <v>-3233800</v>
       </c>
       <c r="E91" s="3">
-        <v>-2389200</v>
+        <v>-2396000</v>
       </c>
       <c r="F91" s="3">
-        <v>-2277400</v>
+        <v>-2283900</v>
       </c>
       <c r="G91" s="3">
-        <v>-3658600</v>
+        <v>-3669100</v>
       </c>
       <c r="H91" s="3">
-        <v>-5812300</v>
+        <v>-5829000</v>
       </c>
       <c r="I91" s="3">
-        <v>-2519400</v>
+        <v>-2526600</v>
       </c>
       <c r="J91" s="3">
-        <v>-2077800</v>
+        <v>-2083700</v>
       </c>
       <c r="K91" s="3">
         <v>-1514000</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2336000</v>
+        <v>-2342700</v>
       </c>
       <c r="E94" s="3">
-        <v>-1344300</v>
+        <v>-1348200</v>
       </c>
       <c r="F94" s="3">
-        <v>-1717600</v>
+        <v>-1722500</v>
       </c>
       <c r="G94" s="3">
-        <v>-3600000</v>
+        <v>-3610300</v>
       </c>
       <c r="H94" s="3">
-        <v>-2933800</v>
+        <v>-2942200</v>
       </c>
       <c r="I94" s="3">
-        <v>-2920800</v>
+        <v>-2929200</v>
       </c>
       <c r="J94" s="3">
-        <v>-788800</v>
+        <v>-791000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -4004,16 +4004,16 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-28200</v>
+        <v>-28300</v>
       </c>
       <c r="H96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="I96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="J96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2990300</v>
+        <v>-2998800</v>
       </c>
       <c r="E100" s="3">
-        <v>-83500</v>
+        <v>-83800</v>
       </c>
       <c r="F100" s="3">
-        <v>7754500</v>
+        <v>7776700</v>
       </c>
       <c r="G100" s="3">
-        <v>-485000</v>
+        <v>-486400</v>
       </c>
       <c r="H100" s="3">
-        <v>-2374000</v>
+        <v>-2380800</v>
       </c>
       <c r="I100" s="3">
-        <v>-694400</v>
+        <v>-696400</v>
       </c>
       <c r="J100" s="3">
-        <v>-723700</v>
+        <v>-725800</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -4211,7 +4211,7 @@
         <v>15200</v>
       </c>
       <c r="F101" s="3">
-        <v>-29300</v>
+        <v>-29400</v>
       </c>
       <c r="G101" s="3">
         <v>1100</v>
@@ -4220,7 +4220,7 @@
         <v>7600</v>
       </c>
       <c r="I101" s="3">
-        <v>-35800</v>
+        <v>-35900</v>
       </c>
       <c r="J101" s="3">
         <v>-14100</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-33600</v>
+        <v>-33700</v>
       </c>
       <c r="E102" s="3">
-        <v>251700</v>
+        <v>252400</v>
       </c>
       <c r="F102" s="3">
-        <v>2941400</v>
+        <v>2949800</v>
       </c>
       <c r="G102" s="3">
-        <v>142100</v>
+        <v>142500</v>
       </c>
       <c r="H102" s="3">
-        <v>-1179400</v>
+        <v>-1182800</v>
       </c>
       <c r="I102" s="3">
-        <v>796400</v>
+        <v>798700</v>
       </c>
       <c r="J102" s="3">
-        <v>902700</v>
+        <v>905300</v>
       </c>
       <c r="K102" s="3">
         <v>-643300</v>

--- a/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>AFLYY</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>28718200</v>
+        <v>32441500</v>
       </c>
       <c r="E8" s="3">
-        <v>15576200</v>
+        <v>28522900</v>
       </c>
       <c r="F8" s="3">
-        <v>12064900</v>
+        <v>15470200</v>
       </c>
       <c r="G8" s="3">
-        <v>29584400</v>
+        <v>11982800</v>
       </c>
       <c r="H8" s="3">
-        <v>28537600</v>
+        <v>29383200</v>
       </c>
       <c r="I8" s="3">
-        <v>28145900</v>
+        <v>28343500</v>
       </c>
       <c r="J8" s="3">
+        <v>27954500</v>
+      </c>
+      <c r="K8" s="3">
         <v>27034900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>27181100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27196400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30539000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>27932000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21402000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15679500</v>
+        <v>17342000</v>
       </c>
       <c r="E9" s="3">
-        <v>8419700</v>
+        <v>15572900</v>
       </c>
       <c r="F9" s="3">
-        <v>7672200</v>
+        <v>8362500</v>
       </c>
       <c r="G9" s="3">
-        <v>14972300</v>
+        <v>7620000</v>
       </c>
       <c r="H9" s="3">
-        <v>14059300</v>
+        <v>14870400</v>
       </c>
       <c r="I9" s="3">
-        <v>14609900</v>
+        <v>13963700</v>
       </c>
       <c r="J9" s="3">
+        <v>14510600</v>
+      </c>
+      <c r="K9" s="3">
         <v>15702400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16938600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16660400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18116400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>34958100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12689700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13038700</v>
+        <v>15099500</v>
       </c>
       <c r="E10" s="3">
-        <v>7156400</v>
+        <v>12950000</v>
       </c>
       <c r="F10" s="3">
-        <v>4392700</v>
+        <v>7107800</v>
       </c>
       <c r="G10" s="3">
-        <v>14612100</v>
+        <v>4362800</v>
       </c>
       <c r="H10" s="3">
-        <v>14478300</v>
+        <v>14512700</v>
       </c>
       <c r="I10" s="3">
-        <v>13536000</v>
+        <v>14379800</v>
       </c>
       <c r="J10" s="3">
+        <v>13443900</v>
+      </c>
+      <c r="K10" s="3">
         <v>11332600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10242500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10536000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12422500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-7026100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8712300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,93 +961,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>101200</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>791000</v>
+        <v>-45400</v>
       </c>
       <c r="F14" s="3">
-        <v>1683300</v>
+        <v>116700</v>
       </c>
       <c r="G14" s="3">
-        <v>166500</v>
+        <v>592200</v>
       </c>
       <c r="H14" s="3">
-        <v>26100</v>
+        <v>165300</v>
       </c>
       <c r="I14" s="3">
-        <v>2094600</v>
+        <v>25900</v>
       </c>
       <c r="J14" s="3">
+        <v>2080300</v>
+      </c>
+      <c r="K14" s="3">
         <v>156700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>148100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-756000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>412700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>442500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>48200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2933500</v>
+        <v>2842200</v>
       </c>
       <c r="E15" s="3">
-        <v>2734400</v>
+        <v>2913600</v>
       </c>
       <c r="F15" s="3">
-        <v>2977000</v>
+        <v>2715800</v>
       </c>
       <c r="G15" s="3">
-        <v>3200100</v>
+        <v>2956800</v>
       </c>
       <c r="H15" s="3">
-        <v>3122800</v>
+        <v>3178300</v>
       </c>
       <c r="I15" s="3">
-        <v>2998800</v>
+        <v>3101600</v>
       </c>
       <c r="J15" s="3">
+        <v>2978400</v>
+      </c>
+      <c r="K15" s="3">
         <v>1709400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1664200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1733500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1873200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1730400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1383400</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>27419000</v>
+        <v>30629200</v>
       </c>
       <c r="E17" s="3">
-        <v>18331200</v>
+        <v>27232600</v>
       </c>
       <c r="F17" s="3">
-        <v>18626100</v>
+        <v>18206600</v>
       </c>
       <c r="G17" s="3">
-        <v>28485400</v>
+        <v>18499400</v>
       </c>
       <c r="H17" s="3">
-        <v>27021900</v>
+        <v>28291600</v>
       </c>
       <c r="I17" s="3">
-        <v>28128500</v>
+        <v>26838100</v>
       </c>
       <c r="J17" s="3">
+        <v>27937200</v>
+      </c>
+      <c r="K17" s="3">
         <v>25829300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26032100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26370600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30810500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28734700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21372800</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1299200</v>
+        <v>1812300</v>
       </c>
       <c r="E18" s="3">
-        <v>-2755100</v>
+        <v>1290400</v>
       </c>
       <c r="F18" s="3">
-        <v>-6561200</v>
+        <v>-2736300</v>
       </c>
       <c r="G18" s="3">
-        <v>1099000</v>
+        <v>-6516600</v>
       </c>
       <c r="H18" s="3">
-        <v>1515700</v>
+        <v>1091500</v>
       </c>
       <c r="I18" s="3">
-        <v>17400</v>
+        <v>1505400</v>
       </c>
       <c r="J18" s="3">
+        <v>17300</v>
+      </c>
+      <c r="K18" s="3">
         <v>1205600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1149000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>825800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-271500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-802600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>29200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-331900</v>
+        <v>167500</v>
       </c>
       <c r="E20" s="3">
-        <v>-517900</v>
+        <v>-329600</v>
       </c>
       <c r="F20" s="3">
-        <v>-558200</v>
+        <v>-514400</v>
       </c>
       <c r="G20" s="3">
-        <v>-278600</v>
+        <v>-554400</v>
       </c>
       <c r="H20" s="3">
-        <v>-356900</v>
+        <v>-276700</v>
       </c>
       <c r="I20" s="3">
-        <v>671400</v>
+        <v>-354500</v>
       </c>
       <c r="J20" s="3">
+        <v>666800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-60900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-672900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-441800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>65800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>146000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-570000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3618400</v>
+        <v>4660300</v>
       </c>
       <c r="E21" s="3">
-        <v>-677700</v>
+        <v>3561700</v>
       </c>
       <c r="F21" s="3">
-        <v>-3990000</v>
+        <v>-704600</v>
       </c>
       <c r="G21" s="3">
-        <v>4090000</v>
+        <v>-4000800</v>
       </c>
       <c r="H21" s="3">
-        <v>4320000</v>
+        <v>4022600</v>
       </c>
       <c r="I21" s="3">
-        <v>3797400</v>
+        <v>4252300</v>
       </c>
       <c r="J21" s="3">
+        <v>3733900</v>
+      </c>
+      <c r="K21" s="3">
         <v>2967200</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>1861200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1265700</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>595200</v>
+        <v>740300</v>
       </c>
       <c r="E22" s="3">
-        <v>588700</v>
+        <v>591100</v>
       </c>
       <c r="F22" s="3">
-        <v>451600</v>
+        <v>584700</v>
       </c>
       <c r="G22" s="3">
-        <v>443900</v>
+        <v>448500</v>
       </c>
       <c r="H22" s="3">
-        <v>472200</v>
+        <v>440900</v>
       </c>
       <c r="I22" s="3">
-        <v>548400</v>
+        <v>469000</v>
       </c>
       <c r="J22" s="3">
+        <v>544700</v>
+      </c>
+      <c r="K22" s="3">
         <v>249200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>360000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>425800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>375500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21300</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>372100</v>
+        <v>1239600</v>
       </c>
       <c r="E23" s="3">
-        <v>-3861700</v>
+        <v>369600</v>
       </c>
       <c r="F23" s="3">
-        <v>-7571000</v>
+        <v>-3835400</v>
       </c>
       <c r="G23" s="3">
-        <v>376500</v>
+        <v>-7519500</v>
       </c>
       <c r="H23" s="3">
-        <v>686600</v>
+        <v>373900</v>
       </c>
       <c r="I23" s="3">
-        <v>140400</v>
+        <v>681900</v>
       </c>
       <c r="J23" s="3">
+        <v>139400</v>
+      </c>
+      <c r="K23" s="3">
         <v>895500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>175600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-631600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1032100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-562100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-424400</v>
+        <v>177200</v>
       </c>
       <c r="E24" s="3">
-        <v>-306800</v>
+        <v>-421500</v>
       </c>
       <c r="F24" s="3">
-        <v>96800</v>
+        <v>-304800</v>
       </c>
       <c r="G24" s="3">
-        <v>82700</v>
+        <v>96200</v>
       </c>
       <c r="H24" s="3">
-        <v>243700</v>
+        <v>82100</v>
       </c>
       <c r="I24" s="3">
-        <v>-22900</v>
+        <v>242100</v>
       </c>
       <c r="J24" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="K24" s="3">
         <v>319900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>212700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1144800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-84100</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>796500</v>
+        <v>1062300</v>
       </c>
       <c r="E26" s="3">
-        <v>-3554800</v>
+        <v>791100</v>
       </c>
       <c r="F26" s="3">
-        <v>-7667800</v>
+        <v>-3530600</v>
       </c>
       <c r="G26" s="3">
-        <v>293800</v>
+        <v>-7615700</v>
       </c>
       <c r="H26" s="3">
-        <v>442900</v>
+        <v>291800</v>
       </c>
       <c r="I26" s="3">
-        <v>163200</v>
+        <v>439800</v>
       </c>
       <c r="J26" s="3">
+        <v>162100</v>
+      </c>
+      <c r="K26" s="3">
         <v>575600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>143900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-188700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1776400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1050800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-478000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>643100</v>
+        <v>834300</v>
       </c>
       <c r="E27" s="3">
-        <v>-3746300</v>
+        <v>638700</v>
       </c>
       <c r="F27" s="3">
-        <v>-7725500</v>
+        <v>-3720900</v>
       </c>
       <c r="G27" s="3">
-        <v>297100</v>
+        <v>-7673000</v>
       </c>
       <c r="H27" s="3">
-        <v>429800</v>
+        <v>295000</v>
       </c>
       <c r="I27" s="3">
-        <v>158900</v>
+        <v>426900</v>
       </c>
       <c r="J27" s="3">
+        <v>157800</v>
+      </c>
+      <c r="K27" s="3">
         <v>568000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>78300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-241100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2039500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1128700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-495900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1542,33 +1602,36 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I29" s="3">
-        <v>-8700</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="K29" s="3">
         <v>293800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>27500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-4400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-145900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-216300</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>331900</v>
+        <v>-167500</v>
       </c>
       <c r="E32" s="3">
-        <v>517900</v>
+        <v>329600</v>
       </c>
       <c r="F32" s="3">
-        <v>558200</v>
+        <v>514400</v>
       </c>
       <c r="G32" s="3">
-        <v>278600</v>
+        <v>554400</v>
       </c>
       <c r="H32" s="3">
-        <v>356900</v>
+        <v>276700</v>
       </c>
       <c r="I32" s="3">
-        <v>-671400</v>
+        <v>354500</v>
       </c>
       <c r="J32" s="3">
+        <v>-666800</v>
+      </c>
+      <c r="K32" s="3">
         <v>60900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>672900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>441800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-65800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-146000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>570000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>643100</v>
+        <v>834300</v>
       </c>
       <c r="E33" s="3">
-        <v>-3746300</v>
+        <v>638700</v>
       </c>
       <c r="F33" s="3">
-        <v>-7725500</v>
+        <v>-3720900</v>
       </c>
       <c r="G33" s="3">
-        <v>297100</v>
+        <v>-7673000</v>
       </c>
       <c r="H33" s="3">
-        <v>429800</v>
+        <v>295000</v>
       </c>
       <c r="I33" s="3">
-        <v>150200</v>
+        <v>426900</v>
       </c>
       <c r="J33" s="3">
+        <v>149100</v>
+      </c>
+      <c r="K33" s="3">
         <v>861800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>105800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-245500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2185500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1345100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-495900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>643100</v>
+        <v>834300</v>
       </c>
       <c r="E35" s="3">
-        <v>-3746300</v>
+        <v>638700</v>
       </c>
       <c r="F35" s="3">
-        <v>-7725500</v>
+        <v>-3720900</v>
       </c>
       <c r="G35" s="3">
-        <v>297100</v>
+        <v>-7673000</v>
       </c>
       <c r="H35" s="3">
-        <v>429800</v>
+        <v>295000</v>
       </c>
       <c r="I35" s="3">
-        <v>150200</v>
+        <v>426900</v>
       </c>
       <c r="J35" s="3">
+        <v>149100</v>
+      </c>
+      <c r="K35" s="3">
         <v>861800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>105800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-245500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2185500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1345100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-495900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,386 +1987,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>14419500</v>
+        <v>6693900</v>
       </c>
       <c r="E41" s="3">
-        <v>7244600</v>
+        <v>19982100</v>
       </c>
       <c r="F41" s="3">
-        <v>6988900</v>
+        <v>7195300</v>
       </c>
       <c r="G41" s="3">
-        <v>4042300</v>
+        <v>6941300</v>
       </c>
       <c r="H41" s="3">
-        <v>3900800</v>
+        <v>4014800</v>
       </c>
       <c r="I41" s="3">
-        <v>10170500</v>
+        <v>3874300</v>
       </c>
       <c r="J41" s="3">
+        <v>10101300</v>
+      </c>
+      <c r="K41" s="3">
         <v>4284900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3284000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3386200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4406800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7510300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4631600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>674600</v>
+        <v>1396300</v>
       </c>
       <c r="E42" s="3">
-        <v>526600</v>
+        <v>670000</v>
       </c>
       <c r="F42" s="3">
-        <v>660500</v>
+        <v>523100</v>
       </c>
       <c r="G42" s="3">
-        <v>870500</v>
+        <v>656000</v>
       </c>
       <c r="H42" s="3">
-        <v>353600</v>
+        <v>864600</v>
       </c>
       <c r="I42" s="3">
-        <v>458100</v>
+        <v>351200</v>
       </c>
       <c r="J42" s="3">
+        <v>455000</v>
+      </c>
+      <c r="K42" s="3">
         <v>141500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1023100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1054900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1233300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1024400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>842600</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4451400</v>
+        <v>2750400</v>
       </c>
       <c r="E43" s="3">
-        <v>2376400</v>
+        <v>4416800</v>
       </c>
       <c r="F43" s="3">
-        <v>2113100</v>
+        <v>2360200</v>
       </c>
       <c r="G43" s="3">
-        <v>2947700</v>
+        <v>2098700</v>
       </c>
       <c r="H43" s="3">
-        <v>2929200</v>
+        <v>2927600</v>
       </c>
       <c r="I43" s="3">
-        <v>5192400</v>
+        <v>2909200</v>
       </c>
       <c r="J43" s="3">
+        <v>5157100</v>
+      </c>
+      <c r="K43" s="3">
         <v>2460200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2354100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2427300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2732100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4172400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4229900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1573400</v>
+        <v>921800</v>
       </c>
       <c r="E44" s="3">
-        <v>617000</v>
+        <v>1562700</v>
       </c>
       <c r="F44" s="3">
-        <v>590800</v>
+        <v>612800</v>
       </c>
       <c r="G44" s="3">
-        <v>801900</v>
+        <v>586800</v>
       </c>
       <c r="H44" s="3">
-        <v>688800</v>
+        <v>796500</v>
       </c>
       <c r="I44" s="3">
-        <v>1212100</v>
+        <v>684100</v>
       </c>
       <c r="J44" s="3">
+        <v>1203900</v>
+      </c>
+      <c r="K44" s="3">
         <v>615900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>562900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>580400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>611300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1144100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1312700</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1861700</v>
+        <v>1006100</v>
       </c>
       <c r="E45" s="3">
-        <v>909700</v>
+        <v>1996100</v>
       </c>
       <c r="F45" s="3">
-        <v>413500</v>
+        <v>903500</v>
       </c>
       <c r="G45" s="3">
-        <v>628900</v>
+        <v>410700</v>
       </c>
       <c r="H45" s="3">
-        <v>613700</v>
+        <v>624600</v>
       </c>
       <c r="I45" s="3">
-        <v>2220800</v>
+        <v>609500</v>
       </c>
       <c r="J45" s="3">
+        <v>2205700</v>
+      </c>
+      <c r="K45" s="3">
         <v>774700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>758600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>782200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1006000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1748000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2028600</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12120300</v>
+        <v>12768500</v>
       </c>
       <c r="E46" s="3">
-        <v>11674200</v>
+        <v>12037900</v>
       </c>
       <c r="F46" s="3">
-        <v>10766700</v>
+        <v>11594800</v>
       </c>
       <c r="G46" s="3">
-        <v>9291300</v>
+        <v>10693500</v>
       </c>
       <c r="H46" s="3">
-        <v>8486100</v>
+        <v>9228100</v>
       </c>
       <c r="I46" s="3">
-        <v>9856000</v>
+        <v>8428400</v>
       </c>
       <c r="J46" s="3">
+        <v>9789000</v>
+      </c>
+      <c r="K46" s="3">
         <v>8277200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7982600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8230900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9494200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8321700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7189700</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1418900</v>
+        <v>1503300</v>
       </c>
       <c r="E47" s="3">
-        <v>1153400</v>
+        <v>1409200</v>
       </c>
       <c r="F47" s="3">
-        <v>1124000</v>
+        <v>1145500</v>
       </c>
       <c r="G47" s="3">
-        <v>1529900</v>
+        <v>1116400</v>
       </c>
       <c r="H47" s="3">
-        <v>1968400</v>
+        <v>1519500</v>
       </c>
       <c r="I47" s="3">
-        <v>1714800</v>
+        <v>1955000</v>
       </c>
       <c r="J47" s="3">
+        <v>1703200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1523300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1424100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1468400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2559900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2246500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2734300</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>37902900</v>
+        <v>20412300</v>
       </c>
       <c r="E48" s="3">
-        <v>18515100</v>
+        <v>37645100</v>
       </c>
       <c r="F48" s="3">
-        <v>18777300</v>
+        <v>18389200</v>
       </c>
       <c r="G48" s="3">
-        <v>19680500</v>
+        <v>18649600</v>
       </c>
       <c r="H48" s="3">
-        <v>19014500</v>
+        <v>19546600</v>
       </c>
       <c r="I48" s="3">
-        <v>38095500</v>
+        <v>18885200</v>
       </c>
       <c r="J48" s="3">
+        <v>37836400</v>
+      </c>
+      <c r="K48" s="3">
         <v>11532800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11017000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11359600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13409400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26308100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6730800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3170700</v>
+        <v>1461100</v>
       </c>
       <c r="E49" s="3">
-        <v>1585400</v>
+        <v>2922200</v>
       </c>
       <c r="F49" s="3">
-        <v>1572300</v>
+        <v>1574600</v>
       </c>
       <c r="G49" s="3">
-        <v>1656100</v>
+        <v>1561600</v>
       </c>
       <c r="H49" s="3">
-        <v>1535300</v>
+        <v>1644800</v>
       </c>
       <c r="I49" s="3">
-        <v>2911800</v>
+        <v>1524900</v>
       </c>
       <c r="J49" s="3">
+        <v>2892000</v>
+      </c>
+      <c r="K49" s="3">
         <v>1397100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1338400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1380000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1355300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2402400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2214800</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1189300</v>
+        <v>1128300</v>
       </c>
       <c r="E52" s="3">
-        <v>458100</v>
+        <v>1181200</v>
       </c>
       <c r="F52" s="3">
-        <v>603900</v>
+        <v>455000</v>
       </c>
       <c r="G52" s="3">
-        <v>1285000</v>
+        <v>599800</v>
       </c>
       <c r="H52" s="3">
-        <v>1243700</v>
+        <v>1276300</v>
       </c>
       <c r="I52" s="3">
-        <v>1579900</v>
+        <v>1235200</v>
       </c>
       <c r="J52" s="3">
+        <v>1569200</v>
+      </c>
+      <c r="K52" s="3">
         <v>2221900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2926400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3017500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3589800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4415100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7902200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>35151100</v>
+        <v>37273300</v>
       </c>
       <c r="E54" s="3">
-        <v>33386200</v>
+        <v>34912000</v>
       </c>
       <c r="F54" s="3">
-        <v>32839900</v>
+        <v>33159100</v>
       </c>
       <c r="G54" s="3">
-        <v>33442800</v>
+        <v>32616600</v>
       </c>
       <c r="H54" s="3">
-        <v>32248000</v>
+        <v>33215300</v>
       </c>
       <c r="I54" s="3">
-        <v>32602700</v>
+        <v>32028700</v>
       </c>
       <c r="J54" s="3">
+        <v>32381000</v>
+      </c>
+      <c r="K54" s="3">
         <v>24952300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24688400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25456400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30408600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29338600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29861800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2637600</v>
+        <v>2644500</v>
       </c>
       <c r="E57" s="3">
-        <v>2013000</v>
+        <v>2619600</v>
       </c>
       <c r="F57" s="3">
-        <v>1561400</v>
+        <v>1999300</v>
       </c>
       <c r="G57" s="3">
-        <v>2588600</v>
+        <v>1550800</v>
       </c>
       <c r="H57" s="3">
-        <v>2670200</v>
+        <v>2571000</v>
       </c>
       <c r="I57" s="3">
-        <v>2573400</v>
+        <v>2652000</v>
       </c>
       <c r="J57" s="3">
+        <v>2555900</v>
+      </c>
+      <c r="K57" s="3">
         <v>2566800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2533900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2612700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2833800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2436500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2916100</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3978100</v>
+        <v>2580700</v>
       </c>
       <c r="E58" s="3">
-        <v>2085900</v>
+        <v>3606300</v>
       </c>
       <c r="F58" s="3">
-        <v>2231700</v>
+        <v>2071700</v>
       </c>
       <c r="G58" s="3">
-        <v>1909600</v>
+        <v>2216500</v>
       </c>
       <c r="H58" s="3">
-        <v>1909600</v>
+        <v>1896600</v>
       </c>
       <c r="I58" s="3">
-        <v>4004200</v>
+        <v>1896600</v>
       </c>
       <c r="J58" s="3">
+        <v>3977000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1019500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2036700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2100000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1973700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3308300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2849900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10443600</v>
+        <v>12010900</v>
       </c>
       <c r="E59" s="3">
-        <v>8660200</v>
+        <v>10408200</v>
       </c>
       <c r="F59" s="3">
-        <v>9022500</v>
+        <v>8601300</v>
       </c>
       <c r="G59" s="3">
-        <v>9265200</v>
+        <v>8961200</v>
       </c>
       <c r="H59" s="3">
-        <v>8849500</v>
+        <v>9202200</v>
       </c>
       <c r="I59" s="3">
-        <v>11568700</v>
+        <v>8789300</v>
       </c>
       <c r="J59" s="3">
+        <v>11490000</v>
+      </c>
+      <c r="K59" s="3">
         <v>7448000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8124400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8377100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10969200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9336300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11662000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14865600</v>
+        <v>17236100</v>
       </c>
       <c r="E60" s="3">
-        <v>12759100</v>
+        <v>14764500</v>
       </c>
       <c r="F60" s="3">
-        <v>12815600</v>
+        <v>12672300</v>
       </c>
       <c r="G60" s="3">
-        <v>13763400</v>
+        <v>12728500</v>
       </c>
       <c r="H60" s="3">
-        <v>13429300</v>
+        <v>13669800</v>
       </c>
       <c r="I60" s="3">
-        <v>13116000</v>
+        <v>13338000</v>
       </c>
       <c r="J60" s="3">
+        <v>13026800</v>
+      </c>
+      <c r="K60" s="3">
         <v>11034400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12694900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13089800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12984800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10790000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10262800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14117000</v>
+        <v>12014100</v>
       </c>
       <c r="E61" s="3">
-        <v>15447800</v>
+        <v>14021000</v>
       </c>
       <c r="F61" s="3">
-        <v>18058100</v>
+        <v>15342700</v>
       </c>
       <c r="G61" s="3">
-        <v>10249900</v>
+        <v>17935300</v>
       </c>
       <c r="H61" s="3">
-        <v>10095400</v>
+        <v>10180200</v>
       </c>
       <c r="I61" s="3">
-        <v>10727600</v>
+        <v>10026700</v>
       </c>
       <c r="J61" s="3">
+        <v>10654600</v>
+      </c>
+      <c r="K61" s="3">
         <v>8085700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7469500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7701800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10282500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10502400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10353700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13381500</v>
+        <v>7482800</v>
       </c>
       <c r="E62" s="3">
-        <v>9331500</v>
+        <v>13290400</v>
       </c>
       <c r="F62" s="3">
-        <v>7778800</v>
+        <v>9268100</v>
       </c>
       <c r="G62" s="3">
-        <v>6927900</v>
+        <v>7725900</v>
       </c>
       <c r="H62" s="3">
-        <v>6766900</v>
+        <v>6880800</v>
       </c>
       <c r="I62" s="3">
-        <v>6518800</v>
+        <v>6720900</v>
       </c>
       <c r="J62" s="3">
+        <v>6474500</v>
+      </c>
+      <c r="K62" s="3">
         <v>4422000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4235200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4366900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4873300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4509500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3911300</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>38419700</v>
+        <v>39489900</v>
       </c>
       <c r="E66" s="3">
-        <v>37547100</v>
+        <v>38158400</v>
       </c>
       <c r="F66" s="3">
-        <v>38662400</v>
+        <v>37291700</v>
       </c>
       <c r="G66" s="3">
-        <v>30957500</v>
+        <v>38399400</v>
       </c>
       <c r="H66" s="3">
-        <v>30304700</v>
+        <v>30747000</v>
       </c>
       <c r="I66" s="3">
-        <v>29982600</v>
+        <v>30098600</v>
       </c>
       <c r="J66" s="3">
+        <v>29778700</v>
+      </c>
+      <c r="K66" s="3">
         <v>23555200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24450400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25210900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27723100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25397800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24300100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-24915300</v>
+        <v>-11178800</v>
       </c>
       <c r="E72" s="3">
-        <v>-12826500</v>
+        <v>-24745900</v>
       </c>
       <c r="F72" s="3">
-        <v>-8860400</v>
+        <v>-12739300</v>
       </c>
       <c r="G72" s="3">
-        <v>-1064200</v>
+        <v>-8800100</v>
       </c>
       <c r="H72" s="3">
-        <v>-1400400</v>
+        <v>-1056900</v>
       </c>
       <c r="I72" s="3">
-        <v>-4575500</v>
+        <v>-1390900</v>
       </c>
       <c r="J72" s="3">
+        <v>-4544300</v>
+      </c>
+      <c r="K72" s="3">
         <v>338400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-480300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-495300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1125600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>442500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1991500</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-3268700</v>
+        <v>-2216500</v>
       </c>
       <c r="E76" s="3">
-        <v>-4160900</v>
+        <v>-3246400</v>
       </c>
       <c r="F76" s="3">
-        <v>-5822400</v>
+        <v>-4132600</v>
       </c>
       <c r="G76" s="3">
-        <v>2485200</v>
+        <v>-5782800</v>
       </c>
       <c r="H76" s="3">
-        <v>1943300</v>
+        <v>2468300</v>
       </c>
       <c r="I76" s="3">
-        <v>2620100</v>
+        <v>1930100</v>
       </c>
       <c r="J76" s="3">
+        <v>2602300</v>
+      </c>
+      <c r="K76" s="3">
         <v>1397100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>238100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>245500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2685500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3940700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5561700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>643100</v>
+        <v>834300</v>
       </c>
       <c r="E81" s="3">
-        <v>-3746300</v>
+        <v>638700</v>
       </c>
       <c r="F81" s="3">
-        <v>-7725500</v>
+        <v>-3720900</v>
       </c>
       <c r="G81" s="3">
-        <v>297100</v>
+        <v>-7673000</v>
       </c>
       <c r="H81" s="3">
-        <v>429800</v>
+        <v>295000</v>
       </c>
       <c r="I81" s="3">
-        <v>150200</v>
+        <v>426900</v>
       </c>
       <c r="J81" s="3">
+        <v>149100</v>
+      </c>
+      <c r="K81" s="3">
         <v>861800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>105800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-245500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2185500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1345100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-495900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2635400</v>
+        <v>2697400</v>
       </c>
       <c r="E83" s="3">
-        <v>2579900</v>
+        <v>2617500</v>
       </c>
       <c r="F83" s="3">
-        <v>3110900</v>
+        <v>2562300</v>
       </c>
       <c r="G83" s="3">
-        <v>3250200</v>
+        <v>3089700</v>
       </c>
       <c r="H83" s="3">
-        <v>3142400</v>
+        <v>3228100</v>
       </c>
       <c r="I83" s="3">
-        <v>3090200</v>
+        <v>3121100</v>
       </c>
       <c r="J83" s="3">
+        <v>3069200</v>
+      </c>
+      <c r="K83" s="3">
         <v>1811700</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>2075400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1919300</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5283800</v>
+        <v>3377200</v>
       </c>
       <c r="E89" s="3">
-        <v>1669100</v>
+        <v>5059800</v>
       </c>
       <c r="F89" s="3">
-        <v>-3075000</v>
+        <v>1657800</v>
       </c>
       <c r="G89" s="3">
-        <v>4238100</v>
+        <v>-3054100</v>
       </c>
       <c r="H89" s="3">
-        <v>4132600</v>
+        <v>4209300</v>
       </c>
       <c r="I89" s="3">
-        <v>4460100</v>
+        <v>4104500</v>
       </c>
       <c r="J89" s="3">
+        <v>4429800</v>
+      </c>
+      <c r="K89" s="3">
         <v>2436300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1077000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1110500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1769200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>934400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>626100</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3233800</v>
+        <v>-3837600</v>
       </c>
       <c r="E91" s="3">
-        <v>-2396000</v>
+        <v>-3023800</v>
       </c>
       <c r="F91" s="3">
-        <v>-2283900</v>
+        <v>-2379700</v>
       </c>
       <c r="G91" s="3">
-        <v>-3669100</v>
+        <v>-2268400</v>
       </c>
       <c r="H91" s="3">
-        <v>-5829000</v>
+        <v>-3644100</v>
       </c>
       <c r="I91" s="3">
-        <v>-2526600</v>
+        <v>-5789300</v>
       </c>
       <c r="J91" s="3">
+        <v>-2509400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2083700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1514000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1561100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1418700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1616300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100400</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2342700</v>
+        <v>-3501500</v>
       </c>
       <c r="E94" s="3">
-        <v>-1348200</v>
+        <v>-2138700</v>
       </c>
       <c r="F94" s="3">
-        <v>-1722500</v>
+        <v>-1339000</v>
       </c>
       <c r="G94" s="3">
-        <v>-3610300</v>
+        <v>-1710700</v>
       </c>
       <c r="H94" s="3">
-        <v>-2942200</v>
+        <v>-3585800</v>
       </c>
       <c r="I94" s="3">
-        <v>-2929200</v>
+        <v>-2922200</v>
       </c>
       <c r="J94" s="3">
+        <v>-2909200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-791000</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-1105300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-269000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,35 +4221,36 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-97300</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-1100</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
-        <v>-28300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-41300</v>
       </c>
-      <c r="I96" s="3">
-        <v>-41300</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-41300</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4025,14 +4258,17 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-2200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2998800</v>
+        <v>-308000</v>
       </c>
       <c r="E100" s="3">
-        <v>-83800</v>
+        <v>-2978400</v>
       </c>
       <c r="F100" s="3">
-        <v>7776700</v>
+        <v>-83200</v>
       </c>
       <c r="G100" s="3">
-        <v>-486400</v>
+        <v>7723800</v>
       </c>
       <c r="H100" s="3">
-        <v>-2380800</v>
+        <v>-483100</v>
       </c>
       <c r="I100" s="3">
-        <v>-696400</v>
+        <v>-2364600</v>
       </c>
       <c r="J100" s="3">
+        <v>-691600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-725800</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>-189000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>476500</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>23900</v>
+        <v>-45400</v>
       </c>
       <c r="E101" s="3">
-        <v>15200</v>
+        <v>23800</v>
       </c>
       <c r="F101" s="3">
-        <v>-29400</v>
+        <v>15100</v>
       </c>
       <c r="G101" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7600</v>
       </c>
-      <c r="I101" s="3">
-        <v>-35900</v>
-      </c>
       <c r="J101" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-14100</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>-43100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3300</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-33700</v>
+        <v>-477700</v>
       </c>
       <c r="E102" s="3">
-        <v>252400</v>
+        <v>-33500</v>
       </c>
       <c r="F102" s="3">
-        <v>2949800</v>
+        <v>250700</v>
       </c>
       <c r="G102" s="3">
-        <v>142500</v>
+        <v>2929800</v>
       </c>
       <c r="H102" s="3">
-        <v>-1182800</v>
+        <v>141600</v>
       </c>
       <c r="I102" s="3">
-        <v>798700</v>
+        <v>-1174700</v>
       </c>
       <c r="J102" s="3">
+        <v>793200</v>
+      </c>
+      <c r="K102" s="3">
         <v>905300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-643300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-663300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>431800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1138600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1640300</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>32441500</v>
+        <v>33249000</v>
       </c>
       <c r="E8" s="3">
-        <v>28522900</v>
+        <v>29232900</v>
       </c>
       <c r="F8" s="3">
-        <v>15470200</v>
+        <v>15855300</v>
       </c>
       <c r="G8" s="3">
-        <v>11982800</v>
+        <v>12281100</v>
       </c>
       <c r="H8" s="3">
-        <v>29383200</v>
+        <v>30114500</v>
       </c>
       <c r="I8" s="3">
-        <v>28343500</v>
+        <v>29049000</v>
       </c>
       <c r="J8" s="3">
-        <v>27954500</v>
+        <v>28650300</v>
       </c>
       <c r="K8" s="3">
         <v>27034900</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>17342000</v>
+        <v>17773700</v>
       </c>
       <c r="E9" s="3">
-        <v>15572900</v>
+        <v>15960500</v>
       </c>
       <c r="F9" s="3">
-        <v>8362500</v>
+        <v>8570600</v>
       </c>
       <c r="G9" s="3">
-        <v>7620000</v>
+        <v>7809700</v>
       </c>
       <c r="H9" s="3">
-        <v>14870400</v>
+        <v>15240600</v>
       </c>
       <c r="I9" s="3">
-        <v>13963700</v>
+        <v>14311300</v>
       </c>
       <c r="J9" s="3">
-        <v>14510600</v>
+        <v>14871700</v>
       </c>
       <c r="K9" s="3">
         <v>15702400</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>15099500</v>
+        <v>15475400</v>
       </c>
       <c r="E10" s="3">
-        <v>12950000</v>
+        <v>13272400</v>
       </c>
       <c r="F10" s="3">
-        <v>7107800</v>
+        <v>7284700</v>
       </c>
       <c r="G10" s="3">
-        <v>4362800</v>
+        <v>4471400</v>
       </c>
       <c r="H10" s="3">
-        <v>14512700</v>
+        <v>14874000</v>
       </c>
       <c r="I10" s="3">
-        <v>14379800</v>
+        <v>14737700</v>
       </c>
       <c r="J10" s="3">
-        <v>13443900</v>
+        <v>13778500</v>
       </c>
       <c r="K10" s="3">
         <v>11332600</v>
@@ -974,22 +974,22 @@
         <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-45400</v>
+        <v>-46500</v>
       </c>
       <c r="F14" s="3">
-        <v>116700</v>
+        <v>119600</v>
       </c>
       <c r="G14" s="3">
-        <v>592200</v>
+        <v>607000</v>
       </c>
       <c r="H14" s="3">
-        <v>165300</v>
+        <v>169500</v>
       </c>
       <c r="I14" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="J14" s="3">
-        <v>2080300</v>
+        <v>2132100</v>
       </c>
       <c r="K14" s="3">
         <v>156700</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2842200</v>
+        <v>2913000</v>
       </c>
       <c r="E15" s="3">
-        <v>2913600</v>
+        <v>2986100</v>
       </c>
       <c r="F15" s="3">
-        <v>2715800</v>
+        <v>2783400</v>
       </c>
       <c r="G15" s="3">
-        <v>2956800</v>
+        <v>3030400</v>
       </c>
       <c r="H15" s="3">
-        <v>3178300</v>
+        <v>3257500</v>
       </c>
       <c r="I15" s="3">
-        <v>3101600</v>
+        <v>3178800</v>
       </c>
       <c r="J15" s="3">
-        <v>2978400</v>
+        <v>3052500</v>
       </c>
       <c r="K15" s="3">
         <v>1709400</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>30629200</v>
+        <v>31391600</v>
       </c>
       <c r="E17" s="3">
-        <v>27232600</v>
+        <v>27910400</v>
       </c>
       <c r="F17" s="3">
-        <v>18206600</v>
+        <v>18659700</v>
       </c>
       <c r="G17" s="3">
-        <v>18499400</v>
+        <v>18959900</v>
       </c>
       <c r="H17" s="3">
-        <v>28291600</v>
+        <v>28995900</v>
       </c>
       <c r="I17" s="3">
-        <v>26838100</v>
+        <v>27506100</v>
       </c>
       <c r="J17" s="3">
-        <v>27937200</v>
+        <v>28632600</v>
       </c>
       <c r="K17" s="3">
         <v>25829300</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1812300</v>
+        <v>1857400</v>
       </c>
       <c r="E18" s="3">
-        <v>1290400</v>
+        <v>1322500</v>
       </c>
       <c r="F18" s="3">
-        <v>-2736300</v>
+        <v>-2804400</v>
       </c>
       <c r="G18" s="3">
-        <v>-6516600</v>
+        <v>-6678800</v>
       </c>
       <c r="H18" s="3">
-        <v>1091500</v>
+        <v>1118700</v>
       </c>
       <c r="I18" s="3">
-        <v>1505400</v>
+        <v>1542900</v>
       </c>
       <c r="J18" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="K18" s="3">
         <v>1205600</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>167500</v>
+        <v>171700</v>
       </c>
       <c r="E20" s="3">
-        <v>-329600</v>
+        <v>-337800</v>
       </c>
       <c r="F20" s="3">
-        <v>-514400</v>
+        <v>-527200</v>
       </c>
       <c r="G20" s="3">
-        <v>-554400</v>
+        <v>-568200</v>
       </c>
       <c r="H20" s="3">
-        <v>-276700</v>
+        <v>-283500</v>
       </c>
       <c r="I20" s="3">
-        <v>-354500</v>
+        <v>-363300</v>
       </c>
       <c r="J20" s="3">
-        <v>666800</v>
+        <v>683400</v>
       </c>
       <c r="K20" s="3">
         <v>-60900</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4660300</v>
+        <v>4793200</v>
       </c>
       <c r="E21" s="3">
-        <v>3561700</v>
+        <v>3666800</v>
       </c>
       <c r="F21" s="3">
-        <v>-704600</v>
+        <v>-706000</v>
       </c>
       <c r="G21" s="3">
-        <v>-4000800</v>
+        <v>-4081000</v>
       </c>
       <c r="H21" s="3">
-        <v>4022600</v>
+        <v>4142900</v>
       </c>
       <c r="I21" s="3">
-        <v>4252300</v>
+        <v>4377800</v>
       </c>
       <c r="J21" s="3">
-        <v>3733900</v>
+        <v>3846100</v>
       </c>
       <c r="K21" s="3">
         <v>2967200</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>740300</v>
+        <v>758700</v>
       </c>
       <c r="E22" s="3">
-        <v>591100</v>
+        <v>605900</v>
       </c>
       <c r="F22" s="3">
-        <v>584700</v>
+        <v>599200</v>
       </c>
       <c r="G22" s="3">
-        <v>448500</v>
+        <v>459700</v>
       </c>
       <c r="H22" s="3">
-        <v>440900</v>
+        <v>451900</v>
       </c>
       <c r="I22" s="3">
-        <v>469000</v>
+        <v>480700</v>
       </c>
       <c r="J22" s="3">
-        <v>544700</v>
+        <v>558200</v>
       </c>
       <c r="K22" s="3">
         <v>249200</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1239600</v>
+        <v>1270400</v>
       </c>
       <c r="E23" s="3">
-        <v>369600</v>
+        <v>378800</v>
       </c>
       <c r="F23" s="3">
-        <v>-3835400</v>
+        <v>-3930900</v>
       </c>
       <c r="G23" s="3">
-        <v>-7519500</v>
+        <v>-7706700</v>
       </c>
       <c r="H23" s="3">
-        <v>373900</v>
+        <v>383200</v>
       </c>
       <c r="I23" s="3">
-        <v>681900</v>
+        <v>698900</v>
       </c>
       <c r="J23" s="3">
-        <v>139400</v>
+        <v>142900</v>
       </c>
       <c r="K23" s="3">
         <v>895500</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>177200</v>
+        <v>181600</v>
       </c>
       <c r="E24" s="3">
-        <v>-421500</v>
+        <v>-432000</v>
       </c>
       <c r="F24" s="3">
-        <v>-304800</v>
+        <v>-312300</v>
       </c>
       <c r="G24" s="3">
-        <v>96200</v>
+        <v>98600</v>
       </c>
       <c r="H24" s="3">
-        <v>82100</v>
+        <v>84200</v>
       </c>
       <c r="I24" s="3">
-        <v>242100</v>
+        <v>248100</v>
       </c>
       <c r="J24" s="3">
-        <v>-22700</v>
+        <v>-23300</v>
       </c>
       <c r="K24" s="3">
         <v>319900</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1062300</v>
+        <v>1088800</v>
       </c>
       <c r="E26" s="3">
-        <v>791100</v>
+        <v>810800</v>
       </c>
       <c r="F26" s="3">
-        <v>-3530600</v>
+        <v>-3618500</v>
       </c>
       <c r="G26" s="3">
-        <v>-7615700</v>
+        <v>-7805300</v>
       </c>
       <c r="H26" s="3">
-        <v>291800</v>
+        <v>299100</v>
       </c>
       <c r="I26" s="3">
-        <v>439800</v>
+        <v>450800</v>
       </c>
       <c r="J26" s="3">
-        <v>162100</v>
+        <v>166100</v>
       </c>
       <c r="K26" s="3">
         <v>575600</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>834300</v>
+        <v>855100</v>
       </c>
       <c r="E27" s="3">
-        <v>638700</v>
+        <v>654600</v>
       </c>
       <c r="F27" s="3">
-        <v>-3720900</v>
+        <v>-3813500</v>
       </c>
       <c r="G27" s="3">
-        <v>-7673000</v>
+        <v>-7864000</v>
       </c>
       <c r="H27" s="3">
-        <v>295000</v>
+        <v>302400</v>
       </c>
       <c r="I27" s="3">
-        <v>426900</v>
+        <v>437500</v>
       </c>
       <c r="J27" s="3">
-        <v>157800</v>
+        <v>161700</v>
       </c>
       <c r="K27" s="3">
         <v>568000</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-8600</v>
+        <v>-8900</v>
       </c>
       <c r="K29" s="3">
         <v>293800</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-167500</v>
+        <v>-171700</v>
       </c>
       <c r="E32" s="3">
-        <v>329600</v>
+        <v>337800</v>
       </c>
       <c r="F32" s="3">
-        <v>514400</v>
+        <v>527200</v>
       </c>
       <c r="G32" s="3">
-        <v>554400</v>
+        <v>568200</v>
       </c>
       <c r="H32" s="3">
-        <v>276700</v>
+        <v>283500</v>
       </c>
       <c r="I32" s="3">
-        <v>354500</v>
+        <v>363300</v>
       </c>
       <c r="J32" s="3">
-        <v>-666800</v>
+        <v>-683400</v>
       </c>
       <c r="K32" s="3">
         <v>60900</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>834300</v>
+        <v>855100</v>
       </c>
       <c r="E33" s="3">
-        <v>638700</v>
+        <v>654600</v>
       </c>
       <c r="F33" s="3">
-        <v>-3720900</v>
+        <v>-3813500</v>
       </c>
       <c r="G33" s="3">
-        <v>-7673000</v>
+        <v>-7864000</v>
       </c>
       <c r="H33" s="3">
-        <v>295000</v>
+        <v>302400</v>
       </c>
       <c r="I33" s="3">
-        <v>426900</v>
+        <v>437500</v>
       </c>
       <c r="J33" s="3">
-        <v>149100</v>
+        <v>152800</v>
       </c>
       <c r="K33" s="3">
         <v>861800</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>834300</v>
+        <v>855100</v>
       </c>
       <c r="E35" s="3">
-        <v>638700</v>
+        <v>654600</v>
       </c>
       <c r="F35" s="3">
-        <v>-3720900</v>
+        <v>-3813500</v>
       </c>
       <c r="G35" s="3">
-        <v>-7673000</v>
+        <v>-7864000</v>
       </c>
       <c r="H35" s="3">
-        <v>295000</v>
+        <v>302400</v>
       </c>
       <c r="I35" s="3">
-        <v>426900</v>
+        <v>437500</v>
       </c>
       <c r="J35" s="3">
-        <v>149100</v>
+        <v>152800</v>
       </c>
       <c r="K35" s="3">
         <v>861800</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6693900</v>
+        <v>6860500</v>
       </c>
       <c r="E41" s="3">
-        <v>19982100</v>
+        <v>20479500</v>
       </c>
       <c r="F41" s="3">
-        <v>7195300</v>
+        <v>7374400</v>
       </c>
       <c r="G41" s="3">
-        <v>6941300</v>
+        <v>7114100</v>
       </c>
       <c r="H41" s="3">
-        <v>4014800</v>
+        <v>4114700</v>
       </c>
       <c r="I41" s="3">
-        <v>3874300</v>
+        <v>3970700</v>
       </c>
       <c r="J41" s="3">
-        <v>10101300</v>
+        <v>10352700</v>
       </c>
       <c r="K41" s="3">
         <v>4284900</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1396300</v>
+        <v>1431000</v>
       </c>
       <c r="E42" s="3">
-        <v>670000</v>
+        <v>686700</v>
       </c>
       <c r="F42" s="3">
-        <v>523100</v>
+        <v>536100</v>
       </c>
       <c r="G42" s="3">
-        <v>656000</v>
+        <v>672300</v>
       </c>
       <c r="H42" s="3">
-        <v>864600</v>
+        <v>886100</v>
       </c>
       <c r="I42" s="3">
-        <v>351200</v>
+        <v>360000</v>
       </c>
       <c r="J42" s="3">
-        <v>455000</v>
+        <v>466300</v>
       </c>
       <c r="K42" s="3">
         <v>141500</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2750400</v>
+        <v>2818800</v>
       </c>
       <c r="E43" s="3">
-        <v>4416800</v>
+        <v>4526800</v>
       </c>
       <c r="F43" s="3">
-        <v>2360200</v>
+        <v>2419000</v>
       </c>
       <c r="G43" s="3">
-        <v>2098700</v>
+        <v>2151000</v>
       </c>
       <c r="H43" s="3">
-        <v>2927600</v>
+        <v>3000500</v>
       </c>
       <c r="I43" s="3">
-        <v>2909200</v>
+        <v>2981700</v>
       </c>
       <c r="J43" s="3">
-        <v>5157100</v>
+        <v>5285500</v>
       </c>
       <c r="K43" s="3">
         <v>2460200</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>921800</v>
+        <v>944800</v>
       </c>
       <c r="E44" s="3">
-        <v>1562700</v>
+        <v>1601600</v>
       </c>
       <c r="F44" s="3">
-        <v>612800</v>
+        <v>628000</v>
       </c>
       <c r="G44" s="3">
-        <v>586800</v>
+        <v>601400</v>
       </c>
       <c r="H44" s="3">
-        <v>796500</v>
+        <v>816300</v>
       </c>
       <c r="I44" s="3">
-        <v>684100</v>
+        <v>701100</v>
       </c>
       <c r="J44" s="3">
-        <v>1203900</v>
+        <v>1233900</v>
       </c>
       <c r="K44" s="3">
         <v>615900</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1006100</v>
+        <v>1031200</v>
       </c>
       <c r="E45" s="3">
-        <v>1996100</v>
+        <v>2045700</v>
       </c>
       <c r="F45" s="3">
-        <v>903500</v>
+        <v>926000</v>
       </c>
       <c r="G45" s="3">
-        <v>410700</v>
+        <v>420900</v>
       </c>
       <c r="H45" s="3">
-        <v>624600</v>
+        <v>640200</v>
       </c>
       <c r="I45" s="3">
-        <v>609500</v>
+        <v>624700</v>
       </c>
       <c r="J45" s="3">
-        <v>2205700</v>
+        <v>2260600</v>
       </c>
       <c r="K45" s="3">
         <v>774700</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12768500</v>
+        <v>13086300</v>
       </c>
       <c r="E46" s="3">
-        <v>12037900</v>
+        <v>12337600</v>
       </c>
       <c r="F46" s="3">
-        <v>11594800</v>
+        <v>11883400</v>
       </c>
       <c r="G46" s="3">
-        <v>10693500</v>
+        <v>10959700</v>
       </c>
       <c r="H46" s="3">
-        <v>9228100</v>
+        <v>9457800</v>
       </c>
       <c r="I46" s="3">
-        <v>8428400</v>
+        <v>8638200</v>
       </c>
       <c r="J46" s="3">
-        <v>9789000</v>
+        <v>10032600</v>
       </c>
       <c r="K46" s="3">
         <v>8277200</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1503300</v>
+        <v>1540700</v>
       </c>
       <c r="E47" s="3">
-        <v>1409200</v>
+        <v>1444300</v>
       </c>
       <c r="F47" s="3">
-        <v>1145500</v>
+        <v>1174100</v>
       </c>
       <c r="G47" s="3">
-        <v>1116400</v>
+        <v>1144200</v>
       </c>
       <c r="H47" s="3">
-        <v>1519500</v>
+        <v>1557300</v>
       </c>
       <c r="I47" s="3">
-        <v>1955000</v>
+        <v>2003600</v>
       </c>
       <c r="J47" s="3">
-        <v>1703200</v>
+        <v>1745600</v>
       </c>
       <c r="K47" s="3">
         <v>1523300</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20412300</v>
+        <v>20920300</v>
       </c>
       <c r="E48" s="3">
-        <v>37645100</v>
+        <v>38582100</v>
       </c>
       <c r="F48" s="3">
-        <v>18389200</v>
+        <v>18846900</v>
       </c>
       <c r="G48" s="3">
-        <v>18649600</v>
+        <v>19113900</v>
       </c>
       <c r="H48" s="3">
-        <v>19546600</v>
+        <v>20033200</v>
       </c>
       <c r="I48" s="3">
-        <v>18885200</v>
+        <v>19355300</v>
       </c>
       <c r="J48" s="3">
-        <v>37836400</v>
+        <v>38778200</v>
       </c>
       <c r="K48" s="3">
         <v>11532800</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1461100</v>
+        <v>1497500</v>
       </c>
       <c r="E49" s="3">
-        <v>2922200</v>
+        <v>2995000</v>
       </c>
       <c r="F49" s="3">
-        <v>1574600</v>
+        <v>1613800</v>
       </c>
       <c r="G49" s="3">
-        <v>1561600</v>
+        <v>1600500</v>
       </c>
       <c r="H49" s="3">
-        <v>1644800</v>
+        <v>1685800</v>
       </c>
       <c r="I49" s="3">
-        <v>1524900</v>
+        <v>1562800</v>
       </c>
       <c r="J49" s="3">
-        <v>2892000</v>
+        <v>2963900</v>
       </c>
       <c r="K49" s="3">
         <v>1397100</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1128300</v>
+        <v>1156300</v>
       </c>
       <c r="E52" s="3">
-        <v>1181200</v>
+        <v>1210600</v>
       </c>
       <c r="F52" s="3">
-        <v>455000</v>
+        <v>466300</v>
       </c>
       <c r="G52" s="3">
-        <v>599800</v>
+        <v>614700</v>
       </c>
       <c r="H52" s="3">
-        <v>1276300</v>
+        <v>1308100</v>
       </c>
       <c r="I52" s="3">
-        <v>1235200</v>
+        <v>1266000</v>
       </c>
       <c r="J52" s="3">
-        <v>1569200</v>
+        <v>1608200</v>
       </c>
       <c r="K52" s="3">
         <v>2221900</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>37273300</v>
+        <v>38201100</v>
       </c>
       <c r="E54" s="3">
-        <v>34912000</v>
+        <v>35781000</v>
       </c>
       <c r="F54" s="3">
-        <v>33159100</v>
+        <v>33984500</v>
       </c>
       <c r="G54" s="3">
-        <v>32616600</v>
+        <v>33428500</v>
       </c>
       <c r="H54" s="3">
-        <v>33215300</v>
+        <v>34042100</v>
       </c>
       <c r="I54" s="3">
-        <v>32028700</v>
+        <v>32825900</v>
       </c>
       <c r="J54" s="3">
-        <v>32381000</v>
+        <v>33187000</v>
       </c>
       <c r="K54" s="3">
         <v>24952300</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2644500</v>
+        <v>2710300</v>
       </c>
       <c r="E57" s="3">
-        <v>2619600</v>
+        <v>2684800</v>
       </c>
       <c r="F57" s="3">
-        <v>1999300</v>
+        <v>2049100</v>
       </c>
       <c r="G57" s="3">
-        <v>1550800</v>
+        <v>1589400</v>
       </c>
       <c r="H57" s="3">
-        <v>2571000</v>
+        <v>2635000</v>
       </c>
       <c r="I57" s="3">
-        <v>2652000</v>
+        <v>2718100</v>
       </c>
       <c r="J57" s="3">
-        <v>2555900</v>
+        <v>2619500</v>
       </c>
       <c r="K57" s="3">
         <v>2566800</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2580700</v>
+        <v>2644900</v>
       </c>
       <c r="E58" s="3">
-        <v>3606300</v>
+        <v>3696100</v>
       </c>
       <c r="F58" s="3">
-        <v>2071700</v>
+        <v>2123300</v>
       </c>
       <c r="G58" s="3">
-        <v>2216500</v>
+        <v>2271700</v>
       </c>
       <c r="H58" s="3">
-        <v>1896600</v>
+        <v>1943800</v>
       </c>
       <c r="I58" s="3">
-        <v>1896600</v>
+        <v>1943800</v>
       </c>
       <c r="J58" s="3">
-        <v>3977000</v>
+        <v>4076000</v>
       </c>
       <c r="K58" s="3">
         <v>1019500</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12010900</v>
+        <v>12309900</v>
       </c>
       <c r="E59" s="3">
-        <v>10408200</v>
+        <v>10667300</v>
       </c>
       <c r="F59" s="3">
-        <v>8601300</v>
+        <v>8815400</v>
       </c>
       <c r="G59" s="3">
-        <v>8961200</v>
+        <v>9184200</v>
       </c>
       <c r="H59" s="3">
-        <v>9202200</v>
+        <v>9431200</v>
       </c>
       <c r="I59" s="3">
-        <v>8789300</v>
+        <v>9008100</v>
       </c>
       <c r="J59" s="3">
-        <v>11490000</v>
+        <v>11776000</v>
       </c>
       <c r="K59" s="3">
         <v>7448000</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>17236100</v>
+        <v>17665100</v>
       </c>
       <c r="E60" s="3">
-        <v>14764500</v>
+        <v>15132000</v>
       </c>
       <c r="F60" s="3">
-        <v>12672300</v>
+        <v>12987700</v>
       </c>
       <c r="G60" s="3">
-        <v>12728500</v>
+        <v>13045300</v>
       </c>
       <c r="H60" s="3">
-        <v>13669800</v>
+        <v>14010000</v>
       </c>
       <c r="I60" s="3">
-        <v>13338000</v>
+        <v>13670000</v>
       </c>
       <c r="J60" s="3">
-        <v>13026800</v>
+        <v>13351000</v>
       </c>
       <c r="K60" s="3">
         <v>11034400</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12014100</v>
+        <v>12313200</v>
       </c>
       <c r="E61" s="3">
-        <v>14021000</v>
+        <v>14370000</v>
       </c>
       <c r="F61" s="3">
-        <v>15342700</v>
+        <v>15724600</v>
       </c>
       <c r="G61" s="3">
-        <v>17935300</v>
+        <v>18381700</v>
       </c>
       <c r="H61" s="3">
-        <v>10180200</v>
+        <v>10433600</v>
       </c>
       <c r="I61" s="3">
-        <v>10026700</v>
+        <v>10276300</v>
       </c>
       <c r="J61" s="3">
-        <v>10654600</v>
+        <v>10919800</v>
       </c>
       <c r="K61" s="3">
         <v>8085700</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7482800</v>
+        <v>7669000</v>
       </c>
       <c r="E62" s="3">
-        <v>13290400</v>
+        <v>13621300</v>
       </c>
       <c r="F62" s="3">
-        <v>9268100</v>
+        <v>9498800</v>
       </c>
       <c r="G62" s="3">
-        <v>7725900</v>
+        <v>7918200</v>
       </c>
       <c r="H62" s="3">
-        <v>6880800</v>
+        <v>7052100</v>
       </c>
       <c r="I62" s="3">
-        <v>6720900</v>
+        <v>6888200</v>
       </c>
       <c r="J62" s="3">
-        <v>6474500</v>
+        <v>6635600</v>
       </c>
       <c r="K62" s="3">
         <v>4422000</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>39489900</v>
+        <v>40472800</v>
       </c>
       <c r="E66" s="3">
-        <v>38158400</v>
+        <v>39108200</v>
       </c>
       <c r="F66" s="3">
-        <v>37291700</v>
+        <v>38220000</v>
       </c>
       <c r="G66" s="3">
-        <v>38399400</v>
+        <v>39355200</v>
       </c>
       <c r="H66" s="3">
-        <v>30747000</v>
+        <v>31512300</v>
       </c>
       <c r="I66" s="3">
-        <v>30098600</v>
+        <v>30847800</v>
       </c>
       <c r="J66" s="3">
-        <v>29778700</v>
+        <v>30519900</v>
       </c>
       <c r="K66" s="3">
         <v>23555200</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-11178800</v>
+        <v>-11457000</v>
       </c>
       <c r="E72" s="3">
-        <v>-24745900</v>
+        <v>-25361800</v>
       </c>
       <c r="F72" s="3">
-        <v>-12739300</v>
+        <v>-13056400</v>
       </c>
       <c r="G72" s="3">
-        <v>-8800100</v>
+        <v>-9019200</v>
       </c>
       <c r="H72" s="3">
-        <v>-1056900</v>
+        <v>-1083200</v>
       </c>
       <c r="I72" s="3">
-        <v>-1390900</v>
+        <v>-1425500</v>
       </c>
       <c r="J72" s="3">
-        <v>-4544300</v>
+        <v>-4657500</v>
       </c>
       <c r="K72" s="3">
         <v>338400</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-2216500</v>
+        <v>-2271700</v>
       </c>
       <c r="E76" s="3">
-        <v>-3246400</v>
+        <v>-3327200</v>
       </c>
       <c r="F76" s="3">
-        <v>-4132600</v>
+        <v>-4235500</v>
       </c>
       <c r="G76" s="3">
-        <v>-5782800</v>
+        <v>-5926800</v>
       </c>
       <c r="H76" s="3">
-        <v>2468300</v>
+        <v>2529800</v>
       </c>
       <c r="I76" s="3">
-        <v>1930100</v>
+        <v>1978200</v>
       </c>
       <c r="J76" s="3">
-        <v>2602300</v>
+        <v>2667100</v>
       </c>
       <c r="K76" s="3">
         <v>1397100</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>834300</v>
+        <v>855100</v>
       </c>
       <c r="E81" s="3">
-        <v>638700</v>
+        <v>654600</v>
       </c>
       <c r="F81" s="3">
-        <v>-3720900</v>
+        <v>-3813500</v>
       </c>
       <c r="G81" s="3">
-        <v>-7673000</v>
+        <v>-7864000</v>
       </c>
       <c r="H81" s="3">
-        <v>295000</v>
+        <v>302400</v>
       </c>
       <c r="I81" s="3">
-        <v>426900</v>
+        <v>437500</v>
       </c>
       <c r="J81" s="3">
-        <v>149100</v>
+        <v>152800</v>
       </c>
       <c r="K81" s="3">
         <v>861800</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2697400</v>
+        <v>2764600</v>
       </c>
       <c r="E83" s="3">
-        <v>2617500</v>
+        <v>2682600</v>
       </c>
       <c r="F83" s="3">
-        <v>2562300</v>
+        <v>2626100</v>
       </c>
       <c r="G83" s="3">
-        <v>3089700</v>
+        <v>3166600</v>
       </c>
       <c r="H83" s="3">
-        <v>3228100</v>
+        <v>3308400</v>
       </c>
       <c r="I83" s="3">
-        <v>3121100</v>
+        <v>3198700</v>
       </c>
       <c r="J83" s="3">
-        <v>3069200</v>
+        <v>3145600</v>
       </c>
       <c r="K83" s="3">
         <v>1811700</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3377200</v>
+        <v>3461300</v>
       </c>
       <c r="E89" s="3">
-        <v>5059800</v>
+        <v>5185800</v>
       </c>
       <c r="F89" s="3">
-        <v>1657800</v>
+        <v>1699100</v>
       </c>
       <c r="G89" s="3">
-        <v>-3054100</v>
+        <v>-3130100</v>
       </c>
       <c r="H89" s="3">
-        <v>4209300</v>
+        <v>4314100</v>
       </c>
       <c r="I89" s="3">
-        <v>4104500</v>
+        <v>4206700</v>
       </c>
       <c r="J89" s="3">
-        <v>4429800</v>
+        <v>4540100</v>
       </c>
       <c r="K89" s="3">
         <v>2436300</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3837600</v>
+        <v>-3933100</v>
       </c>
       <c r="E91" s="3">
-        <v>-3023800</v>
+        <v>-3099100</v>
       </c>
       <c r="F91" s="3">
-        <v>-2379700</v>
+        <v>-2438900</v>
       </c>
       <c r="G91" s="3">
-        <v>-2268400</v>
+        <v>-2324900</v>
       </c>
       <c r="H91" s="3">
-        <v>-3644100</v>
+        <v>-3734800</v>
       </c>
       <c r="I91" s="3">
-        <v>-5789300</v>
+        <v>-5933400</v>
       </c>
       <c r="J91" s="3">
-        <v>-2509400</v>
+        <v>-2571800</v>
       </c>
       <c r="K91" s="3">
         <v>-2083700</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3501500</v>
+        <v>-3588600</v>
       </c>
       <c r="E94" s="3">
-        <v>-2138700</v>
+        <v>-2191900</v>
       </c>
       <c r="F94" s="3">
-        <v>-1339000</v>
+        <v>-1372300</v>
       </c>
       <c r="G94" s="3">
-        <v>-1710700</v>
+        <v>-1753300</v>
       </c>
       <c r="H94" s="3">
-        <v>-3585800</v>
+        <v>-3675000</v>
       </c>
       <c r="I94" s="3">
-        <v>-2922200</v>
+        <v>-2995000</v>
       </c>
       <c r="J94" s="3">
-        <v>-2909200</v>
+        <v>-2981700</v>
       </c>
       <c r="K94" s="3">
         <v>-791000</v>
@@ -4228,7 +4228,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-97300</v>
+        <v>-99700</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4240,13 +4240,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-28100</v>
+        <v>-28800</v>
       </c>
       <c r="I96" s="3">
-        <v>-41100</v>
+        <v>-42100</v>
       </c>
       <c r="J96" s="3">
-        <v>-41100</v>
+        <v>-42100</v>
       </c>
       <c r="K96" s="3">
         <v>-41300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-308000</v>
+        <v>-315700</v>
       </c>
       <c r="E100" s="3">
-        <v>-2978400</v>
+        <v>-3052500</v>
       </c>
       <c r="F100" s="3">
-        <v>-83200</v>
+        <v>-85300</v>
       </c>
       <c r="G100" s="3">
-        <v>7723800</v>
+        <v>7916000</v>
       </c>
       <c r="H100" s="3">
-        <v>-483100</v>
+        <v>-495100</v>
       </c>
       <c r="I100" s="3">
-        <v>-2364600</v>
+        <v>-2423400</v>
       </c>
       <c r="J100" s="3">
-        <v>-691600</v>
+        <v>-708900</v>
       </c>
       <c r="K100" s="3">
         <v>-725800</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-45400</v>
+        <v>-46500</v>
       </c>
       <c r="E101" s="3">
-        <v>23800</v>
+        <v>24400</v>
       </c>
       <c r="F101" s="3">
-        <v>15100</v>
+        <v>15500</v>
       </c>
       <c r="G101" s="3">
-        <v>-29200</v>
+        <v>-29900</v>
       </c>
       <c r="H101" s="3">
         <v>1100</v>
       </c>
       <c r="I101" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="J101" s="3">
-        <v>-35700</v>
+        <v>-36600</v>
       </c>
       <c r="K101" s="3">
         <v>-14100</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-477700</v>
+        <v>-489600</v>
       </c>
       <c r="E102" s="3">
-        <v>-33500</v>
+        <v>-34300</v>
       </c>
       <c r="F102" s="3">
-        <v>250700</v>
+        <v>257000</v>
       </c>
       <c r="G102" s="3">
-        <v>2929800</v>
+        <v>3002700</v>
       </c>
       <c r="H102" s="3">
-        <v>141600</v>
+        <v>145100</v>
       </c>
       <c r="I102" s="3">
-        <v>-1174700</v>
+        <v>-1204000</v>
       </c>
       <c r="J102" s="3">
-        <v>793200</v>
+        <v>813000</v>
       </c>
       <c r="K102" s="3">
         <v>905300</v>

--- a/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AFLYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>AFLYY</t>
   </si>
@@ -656,135 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>38754300</v>
+      </c>
+      <c r="E8" s="3">
         <v>32569600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33181200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28206700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16280000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13563300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30511700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30028600</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>30614100</v>
+      </c>
+      <c r="E9" s="3">
         <v>26330900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26363400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22819300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14366000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14269100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23872700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22959700</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8140200</v>
+      </c>
+      <c r="E10" s="3">
         <v>6238700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6817700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5387400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1914000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-705800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6639000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7068900</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +808,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,9 +835,12 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,63 +865,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E14" s="3">
         <v>139800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>38700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1054200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1814100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>97600</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3585800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2736300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2758900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2588400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2696500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3497200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3352000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3306600</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -914,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36309700</v>
+      </c>
+      <c r="E17" s="3">
         <v>30934900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>31331900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27103800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18156500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19222000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29248100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28336400</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2444500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1634700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1849200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1102900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1876500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5658700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1263600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1692200</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -981,143 +1013,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-389800</v>
+      </c>
+      <c r="E20" s="3">
         <v>391300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>16600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>118600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>520900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>601800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>319800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>478600</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6420100</v>
+      </c>
+      <c r="E21" s="3">
         <v>3979700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4591600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3572700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>299100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2763300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4295800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4520300</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>736200</v>
+      </c>
+      <c r="E22" s="3">
         <v>653300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>663200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>608100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>615300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>507600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>432100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>477400</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2203800</v>
+      </c>
+      <c r="E23" s="3">
         <v>593200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1275600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>378300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4066900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8582300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>414100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>739600</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>144400</v>
+      </c>
+      <c r="E24" s="3">
         <v>87000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>181300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-416800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-320700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>108900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>85300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>256500</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1142,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2059400</v>
+      </c>
+      <c r="E26" s="3">
         <v>506300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1094300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>795100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3746200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8691100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>328800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>483200</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1798800</v>
+      </c>
+      <c r="E27" s="3">
         <v>252600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>853300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>631600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3915600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8685000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>306400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>452300</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1223,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1250,9 +1310,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1277,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,63 +1370,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>389800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-391300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-16600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-118600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-520900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-601800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-319800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-478600</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1870400</v>
+      </c>
+      <c r="E33" s="3">
         <v>328200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1032400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>778000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3743900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8685000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>325400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>480900</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1385,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1870400</v>
+      </c>
+      <c r="E35" s="3">
         <v>328200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1032400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>778000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3743900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8685000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>325400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>480900</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1471,251 +1556,279 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5534800</v>
+      </c>
+      <c r="E41" s="3">
         <v>4999500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6846500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7081300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7571900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7856900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4169000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4104600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1229900</v>
+        <v>1262200</v>
       </c>
       <c r="E42" s="3">
-        <v>1390500</v>
+        <v>961800</v>
       </c>
       <c r="F42" s="3">
+        <v>1161700</v>
+      </c>
+      <c r="G42" s="3">
         <v>691500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>539100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>349800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>542000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>53800</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3179500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2670000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2854000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2469800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2490600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2385300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3055800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3095900</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1164700</v>
+      </c>
+      <c r="E44" s="3">
         <v>992900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>942900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>772700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>644800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>664200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>827100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>724800</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>792000</v>
+        <v>982700</v>
       </c>
       <c r="E45" s="3">
-        <v>736200</v>
+        <v>1060200</v>
       </c>
       <c r="F45" s="3">
+        <v>965000</v>
+      </c>
+      <c r="G45" s="3">
         <v>644400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>763100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>305800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>404000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>369800</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12401100</v>
+      </c>
+      <c r="E46" s="3">
         <v>10958700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13059600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11904500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12201800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12104000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9582500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8929500</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1345500</v>
+      </c>
+      <c r="E47" s="3">
         <v>1278600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1163900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1184100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>851800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>867300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1087400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1110600</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29097100</v>
+      </c>
+      <c r="E48" s="3">
         <v>22230000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20877600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18613900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19351800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21109500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20297400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20008000</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1986600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1646100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1663500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1528300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1657000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1767600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1708000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1615500</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1740,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1767,36 +1883,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>352200</v>
+      </c>
+      <c r="E52" s="3">
         <v>410000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>339300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>353700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>341200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>588400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1077300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1489600</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1821,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46313300</v>
+      </c>
+      <c r="E54" s="3">
         <v>37431400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38123100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34525000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>34894800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36918700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>34491100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33932900</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1862,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1875,170 +2004,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3197100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2704800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2590600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2103900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1755400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2669700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2809700</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3242900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2768400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2791000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1852100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2333700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2661800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2052500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2089500</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10689200</v>
+      </c>
+      <c r="E59" s="3">
         <v>8991600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8914600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8053900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7778900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8455000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8228000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8010100</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20092800</v>
+      </c>
+      <c r="E60" s="3">
         <v>16845400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17629000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14600800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13335600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14407300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14194800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14131000</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14987700</v>
+      </c>
+      <c r="E61" s="3">
         <v>12412300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12305700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13867700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16162900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20352300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10612700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10658300</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6262800</v>
+      </c>
+      <c r="E62" s="3">
         <v>5568900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5737800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6923200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7481000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6126000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4396800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4657700</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2063,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2090,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2117,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43537600</v>
+      </c>
+      <c r="E66" s="3">
         <v>36604200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37570500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37175400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39234600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43453200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31911100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31874300</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2184,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2211,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2238,9 +2405,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1952600</v>
+      </c>
+      <c r="E72" s="3">
         <v>400700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1109800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>852800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3664300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8599400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>404000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>561000</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2319,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2346,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2373,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>349900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1826300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2267000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3210400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4348900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-6545600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2563100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2044900</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2427,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1870400</v>
+      </c>
+      <c r="E81" s="3">
         <v>328200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1032400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>778000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3743900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8685000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>325400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>480900</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2500,35 +2697,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3612800</v>
+      </c>
+      <c r="E83" s="3">
         <v>2747700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2730200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2686800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2639600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3118000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3131000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3102800</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2553,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2580,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2607,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2634,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2661,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5935200</v>
+      </c>
+      <c r="E89" s="3">
         <v>3619400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3985900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5003700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1744600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3456900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4371000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4348500</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2702,35 +2921,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5223700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3859600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3925100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2990300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2504300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2567600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3784100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3256200</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2755,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2782,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3345100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2865700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3334800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2115000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1409100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1936400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3723500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3095900</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2823,23 +3055,24 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E96" s="3">
         <v>73500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>168000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>269300</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -2849,9 +3082,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2876,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2903,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2930,88 +3172,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2689900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2188600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2945400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-87600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8742500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-501600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2505200</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E101" s="3">
         <v>35200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-46400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>23500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>15900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-33000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8000</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1399700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-488600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>263800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3316200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>147000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1244600</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
